--- a/research/traditional_assets/database/data/new_zealand/new_zealand_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_publishing_newspapers.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08822489048636288</v>
+        <v>0.08801026079300107</v>
       </c>
       <c r="C2">
-        <v>168.9565668879155</v>
+        <v>167.5455313185346</v>
       </c>
       <c r="D2">
-        <v>164.2965668879155</v>
+        <v>164.7025313185346</v>
       </c>
       <c r="E2">
-        <v>-70.90000000000001</v>
+        <v>-69.08300000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.817</v>
       </c>
       <c r="G2">
         <v>4.66</v>
@@ -1457,28 +1457,28 @@
         <v>2.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.09139509999999999</v>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>2.4086049</v>
       </c>
       <c r="O2">
-        <v>0.7000000000000001</v>
+        <v>0.6744093720000001</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>1.734195528</v>
       </c>
       <c r="Q2">
-        <v>19.3</v>
+        <v>19.234195528</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08822489048636288</v>
+        <v>0.08853343514444553</v>
       </c>
       <c r="T2">
-        <v>0.9797896186226994</v>
+        <v>0.9869153613035918</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>27.35376404205477</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08801026079300107</v>
+        <v>0.08779563109963925</v>
       </c>
       <c r="C3">
-        <v>167.5455313185346</v>
+        <v>166.1365069336446</v>
       </c>
       <c r="D3">
-        <v>164.7025313185346</v>
+        <v>165.1105069336446</v>
       </c>
       <c r="E3">
-        <v>-69.08300000000001</v>
+        <v>-67.26600000000001</v>
       </c>
       <c r="F3">
-        <v>1.817</v>
+        <v>3.634</v>
       </c>
       <c r="G3">
         <v>4.66</v>
@@ -1539,28 +1539,28 @@
         <v>2.5</v>
       </c>
       <c r="M3">
-        <v>0.09139509999999999</v>
+        <v>0.1827902</v>
       </c>
       <c r="N3">
-        <v>2.4086049</v>
+        <v>2.3172098</v>
       </c>
       <c r="O3">
-        <v>0.6744093720000001</v>
+        <v>0.6488187440000001</v>
       </c>
       <c r="P3">
-        <v>1.734195528</v>
+        <v>1.668391056</v>
       </c>
       <c r="Q3">
-        <v>19.234195528</v>
+        <v>19.168391056</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08853343514444553</v>
+        <v>0.08884827663228495</v>
       </c>
       <c r="T3">
-        <v>0.9869153613035918</v>
+        <v>0.9941865273045023</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>27.35376404205477</v>
+        <v>13.67688202102739</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08779563109963925</v>
+        <v>0.08765012140627744</v>
       </c>
       <c r="C4">
-        <v>166.1365069336446</v>
+        <v>164.5972483846309</v>
       </c>
       <c r="D4">
-        <v>165.1105069336446</v>
+        <v>165.3882483846309</v>
       </c>
       <c r="E4">
-        <v>-67.26600000000001</v>
+        <v>-65.44900000000001</v>
       </c>
       <c r="F4">
-        <v>3.634</v>
+        <v>5.451</v>
       </c>
       <c r="G4">
         <v>4.66</v>
@@ -1621,45 +1621,45 @@
         <v>2.5</v>
       </c>
       <c r="M4">
-        <v>0.1827902</v>
+        <v>0.2916285</v>
       </c>
       <c r="N4">
-        <v>2.3172098</v>
+        <v>2.2083715</v>
       </c>
       <c r="O4">
-        <v>0.6488187440000001</v>
+        <v>0.6183440200000001</v>
       </c>
       <c r="P4">
-        <v>1.668391056</v>
+        <v>1.59002748</v>
       </c>
       <c r="Q4">
-        <v>19.168391056</v>
+        <v>19.09002748</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08884827663228495</v>
+        <v>0.08916960969719323</v>
       </c>
       <c r="T4">
-        <v>0.9941865273045023</v>
+        <v>1.001607614253885</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V4">
         <v>0.28</v>
       </c>
       <c r="W4">
-        <v>0.036216</v>
+        <v>0.03852</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y4">
-        <v>13.67688202102739</v>
+        <v>8.572550350874486</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08765012140627744</v>
+        <v>0.08748157171291561</v>
       </c>
       <c r="C5">
-        <v>164.5972483846309</v>
+        <v>163.1031377412098</v>
       </c>
       <c r="D5">
-        <v>165.3882483846309</v>
+        <v>165.7111377412098</v>
       </c>
       <c r="E5">
-        <v>-65.44900000000001</v>
+        <v>-63.63200000000001</v>
       </c>
       <c r="F5">
-        <v>5.451</v>
+        <v>7.268</v>
       </c>
       <c r="G5">
         <v>4.66</v>
@@ -1703,45 +1703,45 @@
         <v>2.5</v>
       </c>
       <c r="M5">
-        <v>0.2916285</v>
+        <v>0.3946524</v>
       </c>
       <c r="N5">
-        <v>2.2083715</v>
+        <v>2.1053476</v>
       </c>
       <c r="O5">
-        <v>0.6183440200000001</v>
+        <v>0.5894973280000001</v>
       </c>
       <c r="P5">
-        <v>1.59002748</v>
+        <v>1.515850272</v>
       </c>
       <c r="Q5">
-        <v>19.09002748</v>
+        <v>19.015850272</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08916960969719323</v>
+        <v>0.08949763720095377</v>
       </c>
       <c r="T5">
-        <v>1.001607614253885</v>
+        <v>1.00918330718138</v>
       </c>
       <c r="U5">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V5">
         <v>0.28</v>
       </c>
       <c r="W5">
-        <v>0.03852</v>
+        <v>0.039096</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y5">
-        <v>8.572550350874486</v>
+        <v>6.334688449886533</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08748157171291561</v>
+        <v>0.08733174201955379</v>
       </c>
       <c r="C6">
-        <v>163.1031377412098</v>
+        <v>161.5742256745576</v>
       </c>
       <c r="D6">
-        <v>165.7111377412098</v>
+        <v>165.9992256745576</v>
       </c>
       <c r="E6">
-        <v>-63.63200000000001</v>
+        <v>-61.815</v>
       </c>
       <c r="F6">
-        <v>7.268</v>
+        <v>9.084999999999999</v>
       </c>
       <c r="G6">
         <v>4.66</v>
@@ -1785,45 +1785,45 @@
         <v>2.5</v>
       </c>
       <c r="M6">
-        <v>0.3946524</v>
+        <v>0.5024004999999999</v>
       </c>
       <c r="N6">
-        <v>2.1053476</v>
+        <v>1.9975995</v>
       </c>
       <c r="O6">
-        <v>0.5894973280000001</v>
+        <v>0.5593278600000001</v>
       </c>
       <c r="P6">
-        <v>1.515850272</v>
+        <v>1.43827164</v>
       </c>
       <c r="Q6">
-        <v>19.015850272</v>
+        <v>18.93827164</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08949763720095377</v>
+        <v>0.08983257054689874</v>
       </c>
       <c r="T6">
-        <v>1.00918330718138</v>
+        <v>1.016918488381033</v>
       </c>
       <c r="U6">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V6">
         <v>0.28</v>
       </c>
       <c r="W6">
-        <v>0.039096</v>
+        <v>0.039816</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y6">
-        <v>6.334688449886533</v>
+        <v>4.976109697343057</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08733174201955379</v>
+        <v>0.08741231232619197</v>
       </c>
       <c r="C7">
-        <v>161.5742256745576</v>
+        <v>159.602183183165</v>
       </c>
       <c r="D7">
-        <v>165.9992256745576</v>
+        <v>165.844183183165</v>
       </c>
       <c r="E7">
-        <v>-61.815</v>
+        <v>-59.998</v>
       </c>
       <c r="F7">
-        <v>9.084999999999999</v>
+        <v>10.902</v>
       </c>
       <c r="G7">
         <v>4.66</v>
@@ -1867,45 +1867,45 @@
         <v>2.5</v>
       </c>
       <c r="M7">
-        <v>0.5024004999999999</v>
+        <v>0.6682926</v>
       </c>
       <c r="N7">
-        <v>1.9975995</v>
+        <v>1.8317074</v>
       </c>
       <c r="O7">
-        <v>0.5593278600000001</v>
+        <v>0.512878072</v>
       </c>
       <c r="P7">
-        <v>1.43827164</v>
+        <v>1.318829328</v>
       </c>
       <c r="Q7">
-        <v>18.93827164</v>
+        <v>18.818829328</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08983257054689874</v>
+        <v>0.09017463013424679</v>
       </c>
       <c r="T7">
-        <v>1.016918488381033</v>
+        <v>1.024818247904083</v>
       </c>
       <c r="U7">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V7">
         <v>0.28</v>
       </c>
       <c r="W7">
-        <v>0.039816</v>
+        <v>0.044136</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>4.976109697343057</v>
+        <v>3.740876376605098</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08741231232619197</v>
+        <v>0.08741800263283016</v>
       </c>
       <c r="C8">
-        <v>159.602183183165</v>
+        <v>157.7742442006816</v>
       </c>
       <c r="D8">
-        <v>165.844183183165</v>
+        <v>165.8332442006816</v>
       </c>
       <c r="E8">
-        <v>-59.998</v>
+        <v>-58.18100000000001</v>
       </c>
       <c r="F8">
-        <v>10.902</v>
+        <v>12.719</v>
       </c>
       <c r="G8">
         <v>4.66</v>
@@ -1949,45 +1949,45 @@
         <v>2.5</v>
       </c>
       <c r="M8">
-        <v>0.6682925999999999</v>
+        <v>0.8152879</v>
       </c>
       <c r="N8">
-        <v>1.8317074</v>
+        <v>1.6847121</v>
       </c>
       <c r="O8">
-        <v>0.512878072</v>
+        <v>0.4717193880000001</v>
       </c>
       <c r="P8">
-        <v>1.318829328</v>
+        <v>1.212992712</v>
       </c>
       <c r="Q8">
-        <v>18.818829328</v>
+        <v>18.712992712</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09017463013424679</v>
+        <v>0.09052404584175286</v>
       </c>
       <c r="T8">
-        <v>1.024818247904083</v>
+        <v>1.032887894728704</v>
       </c>
       <c r="U8">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V8">
         <v>0.28</v>
       </c>
       <c r="W8">
-        <v>0.044136</v>
+        <v>0.046152</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y8">
-        <v>3.740876376605098</v>
+        <v>3.066401451560854</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08741800263283016</v>
+        <v>0.08797665293946835</v>
       </c>
       <c r="C9">
-        <v>157.7742442006816</v>
+        <v>154.8902811154067</v>
       </c>
       <c r="D9">
-        <v>165.8332442006816</v>
+        <v>164.7662811154067</v>
       </c>
       <c r="E9">
-        <v>-58.181</v>
+        <v>-56.364</v>
       </c>
       <c r="F9">
-        <v>12.719</v>
+        <v>14.536</v>
       </c>
       <c r="G9">
         <v>4.66</v>
@@ -2031,45 +2031,45 @@
         <v>2.5</v>
       </c>
       <c r="M9">
-        <v>0.8152879000000002</v>
+        <v>1.1018288</v>
       </c>
       <c r="N9">
-        <v>1.6847121</v>
+        <v>1.3981712</v>
       </c>
       <c r="O9">
-        <v>0.471719388</v>
+        <v>0.391487936</v>
       </c>
       <c r="P9">
-        <v>1.212992712</v>
+        <v>1.006683264</v>
       </c>
       <c r="Q9">
-        <v>18.712992712</v>
+        <v>18.506683264</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09052404584175286</v>
+        <v>0.09088105754290038</v>
       </c>
       <c r="T9">
-        <v>1.032887894728704</v>
+        <v>1.041132968658208</v>
       </c>
       <c r="U9">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V9">
         <v>0.28</v>
       </c>
       <c r="W9">
-        <v>0.046152</v>
+        <v>0.054576</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y9">
-        <v>3.066401451560853</v>
+        <v>2.268955031852498</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08797665293946835</v>
+        <v>0.08794562324610654</v>
       </c>
       <c r="C10">
-        <v>154.8902811154067</v>
+        <v>153.1321843046084</v>
       </c>
       <c r="D10">
-        <v>164.7662811154067</v>
+        <v>164.8251843046084</v>
       </c>
       <c r="E10">
-        <v>-56.364</v>
+        <v>-54.54700000000001</v>
       </c>
       <c r="F10">
-        <v>14.536</v>
+        <v>16.353</v>
       </c>
       <c r="G10">
         <v>4.66</v>
@@ -2113,28 +2113,28 @@
         <v>2.5</v>
       </c>
       <c r="M10">
-        <v>1.1018288</v>
+        <v>1.2395574</v>
       </c>
       <c r="N10">
-        <v>1.3981712</v>
+        <v>1.2604426</v>
       </c>
       <c r="O10">
-        <v>0.391487936</v>
+        <v>0.352923928</v>
       </c>
       <c r="P10">
-        <v>1.006683264</v>
+        <v>0.9075186719999999</v>
       </c>
       <c r="Q10">
-        <v>18.506683264</v>
+        <v>18.407518672</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09088105754290038</v>
+        <v>0.09124591565506213</v>
       </c>
       <c r="T10">
-        <v>1.041132968658208</v>
+        <v>1.049559253003745</v>
       </c>
       <c r="U10">
         <v>0.07580000000000001</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>2.268955031852498</v>
+        <v>2.01684891720222</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,81 +2159,81 @@
     </row>
     <row r="11">
       <c r="A11">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="B11">
+        <v>0.08893699355274472</v>
+      </c>
+      <c r="C11">
+        <v>149.4538678494435</v>
+      </c>
+      <c r="D11">
+        <v>162.9638678494435</v>
+      </c>
+      <c r="E11">
+        <v>-52.73</v>
+      </c>
+      <c r="F11">
+        <v>18.17</v>
+      </c>
+      <c r="G11">
+        <v>4.66</v>
+      </c>
+      <c r="H11">
+        <v>110.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
+      <c r="K11">
+        <v>17.5</v>
+      </c>
+      <c r="L11">
+        <v>2.5</v>
+      </c>
+      <c r="M11">
+        <v>1.6353</v>
+      </c>
+      <c r="N11">
+        <v>0.8647000000000002</v>
+      </c>
+      <c r="O11">
+        <v>0.2421160000000001</v>
+      </c>
+      <c r="P11">
+        <v>0.6225840000000001</v>
+      </c>
+      <c r="Q11">
+        <v>18.122584</v>
+      </c>
+      <c r="R11">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S11">
+        <v>0.09161888172527191</v>
+      </c>
+      <c r="T11">
+        <v>1.058172788112515</v>
+      </c>
+      <c r="U11">
         <v>0.09</v>
-      </c>
-      <c r="B11">
-        <v>0.08794562324610654</v>
-      </c>
-      <c r="C11">
-        <v>153.1321843046084</v>
-      </c>
-      <c r="D11">
-        <v>164.8251843046084</v>
-      </c>
-      <c r="E11">
-        <v>-54.54700000000001</v>
-      </c>
-      <c r="F11">
-        <v>16.353</v>
-      </c>
-      <c r="G11">
-        <v>4.66</v>
-      </c>
-      <c r="H11">
-        <v>110.8</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>20</v>
-      </c>
-      <c r="K11">
-        <v>17.5</v>
-      </c>
-      <c r="L11">
-        <v>2.5</v>
-      </c>
-      <c r="M11">
-        <v>1.2395574</v>
-      </c>
-      <c r="N11">
-        <v>1.2604426</v>
-      </c>
-      <c r="O11">
-        <v>0.352923928</v>
-      </c>
-      <c r="P11">
-        <v>0.9075186719999999</v>
-      </c>
-      <c r="Q11">
-        <v>18.407518672</v>
-      </c>
-      <c r="R11">
-        <v>0.0989010989010989</v>
-      </c>
-      <c r="S11">
-        <v>0.09124591565506213</v>
-      </c>
-      <c r="T11">
-        <v>1.049559253003745</v>
-      </c>
-      <c r="U11">
-        <v>0.07580000000000001</v>
       </c>
       <c r="V11">
         <v>0.28</v>
       </c>
       <c r="W11">
-        <v>0.054576</v>
+        <v>0.0648</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.01684891720222</v>
+        <v>1.528771479239284</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08893699355274472</v>
+        <v>0.09436902078841278</v>
       </c>
       <c r="C12">
-        <v>149.4538678494435</v>
+        <v>138.1408795412628</v>
       </c>
       <c r="D12">
-        <v>162.9638678494435</v>
+        <v>153.4678795412628</v>
       </c>
       <c r="E12">
-        <v>-52.73</v>
+        <v>-50.91300000000001</v>
       </c>
       <c r="F12">
-        <v>18.17</v>
+        <v>19.987</v>
       </c>
       <c r="G12">
         <v>4.66</v>
@@ -2277,45 +2277,45 @@
         <v>2.5</v>
       </c>
       <c r="M12">
-        <v>1.6353</v>
+        <v>2.9340916</v>
       </c>
       <c r="N12">
-        <v>0.8647000000000002</v>
+        <v>-0.4340915999999999</v>
       </c>
       <c r="O12">
-        <v>0.2421160000000001</v>
+        <v>-0.121545648</v>
       </c>
       <c r="P12">
-        <v>0.6225840000000001</v>
+        <v>-0.3125459519999999</v>
       </c>
       <c r="Q12">
-        <v>18.122584</v>
+        <v>17.187454048</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09161888172527191</v>
+        <v>0.09221744372595031</v>
       </c>
       <c r="T12">
-        <v>1.058172788112515</v>
+        <v>1.071996390899545</v>
       </c>
       <c r="U12">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V12">
-        <v>0.28</v>
+        <v>0.2385746920784614</v>
       </c>
       <c r="W12">
-        <v>0.0648</v>
+        <v>0.1117772352028819</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y12">
-        <v>1.528771479239284</v>
+        <v>0.8520524717087906</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09436902078841278</v>
+        <v>0.102158431848146</v>
       </c>
       <c r="C13">
-        <v>138.1408795412628</v>
+        <v>124.4891975764503</v>
       </c>
       <c r="D13">
-        <v>153.4678795412628</v>
+        <v>141.6331975764503</v>
       </c>
       <c r="E13">
-        <v>-50.91300000000001</v>
+        <v>-49.096</v>
       </c>
       <c r="F13">
-        <v>19.987</v>
+        <v>21.804</v>
       </c>
       <c r="G13">
         <v>4.66</v>
@@ -2359,45 +2359,45 @@
         <v>2.5</v>
       </c>
       <c r="M13">
-        <v>2.9340916</v>
+        <v>4.3782432</v>
       </c>
       <c r="N13">
-        <v>-0.4340915999999999</v>
+        <v>-1.8782432</v>
       </c>
       <c r="O13">
-        <v>-0.121545648</v>
+        <v>-0.5259080960000001</v>
       </c>
       <c r="P13">
-        <v>-0.3125459519999999</v>
+        <v>-1.352335104</v>
       </c>
       <c r="Q13">
-        <v>17.187454048</v>
+        <v>16.147664896</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09221744372595031</v>
+        <v>0.09308515451798745</v>
       </c>
       <c r="T13">
-        <v>1.071996390899545</v>
+        <v>1.092035901108255</v>
       </c>
       <c r="U13">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V13">
-        <v>0.2385746920784614</v>
+        <v>0.1598814794025147</v>
       </c>
       <c r="W13">
-        <v>0.1117772352028819</v>
+        <v>0.1686957989359751</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y13">
-        <v>0.8520524717087906</v>
+        <v>0.5710052835804096</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.102158431848146</v>
+        <v>0.1037084318481459</v>
       </c>
       <c r="C14">
-        <v>124.4891975764503</v>
+        <v>120.5316858529724</v>
       </c>
       <c r="D14">
-        <v>141.6331975764503</v>
+        <v>139.4926858529724</v>
       </c>
       <c r="E14">
-        <v>-49.096</v>
+        <v>-47.27900000000001</v>
       </c>
       <c r="F14">
-        <v>21.804</v>
+        <v>23.621</v>
       </c>
       <c r="G14">
         <v>4.66</v>
@@ -2441,37 +2441,37 @@
         <v>2.5</v>
       </c>
       <c r="M14">
-        <v>4.3782432</v>
+        <v>4.7430968</v>
       </c>
       <c r="N14">
-        <v>-1.8782432</v>
+        <v>-2.2430968</v>
       </c>
       <c r="O14">
-        <v>-0.5259080960000001</v>
+        <v>-0.6280671040000001</v>
       </c>
       <c r="P14">
-        <v>-1.352335104</v>
+        <v>-1.615029696</v>
       </c>
       <c r="Q14">
-        <v>16.147664896</v>
+        <v>15.884970304</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09308515451798745</v>
+        <v>0.0936286620411827</v>
       </c>
       <c r="T14">
-        <v>1.092035901108255</v>
+        <v>1.104588037902603</v>
       </c>
       <c r="U14">
         <v>0.2008</v>
       </c>
       <c r="V14">
-        <v>0.1598814794025147</v>
+        <v>0.1475829040638597</v>
       </c>
       <c r="W14">
-        <v>0.1686957989359751</v>
+        <v>0.171165352863977</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.5710052835804096</v>
+        <v>0.5270818002280704</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1037084318481459</v>
+        <v>0.1102792478272328</v>
       </c>
       <c r="C15">
-        <v>120.5316858529724</v>
+        <v>110.3157885373775</v>
       </c>
       <c r="D15">
-        <v>139.4926858529724</v>
+        <v>131.0937885373775</v>
       </c>
       <c r="E15">
-        <v>-47.27900000000001</v>
+        <v>-45.462</v>
       </c>
       <c r="F15">
-        <v>23.621</v>
+        <v>25.438</v>
       </c>
       <c r="G15">
         <v>4.66</v>
@@ -2523,45 +2523,45 @@
         <v>2.5</v>
       </c>
       <c r="M15">
-        <v>4.7430968</v>
+        <v>5.998280400000001</v>
       </c>
       <c r="N15">
-        <v>-2.2430968</v>
+        <v>-3.498280400000001</v>
       </c>
       <c r="O15">
-        <v>-0.6280671040000001</v>
+        <v>-0.9795185120000003</v>
       </c>
       <c r="P15">
-        <v>-1.615029696</v>
+        <v>-2.518761888</v>
       </c>
       <c r="Q15">
-        <v>15.884970304</v>
+        <v>14.981238112</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0936286620411827</v>
+        <v>0.09432529297083238</v>
       </c>
       <c r="T15">
-        <v>1.104588037902603</v>
+        <v>1.120676512028461</v>
       </c>
       <c r="U15">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.1475829040638597</v>
+        <v>0.1167001129190293</v>
       </c>
       <c r="W15">
-        <v>0.171165352863977</v>
+        <v>0.2082821133736929</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y15">
-        <v>0.5270818002280704</v>
+        <v>0.4167861175679616</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1102792478272328</v>
+        <v>0.1121792478272328</v>
       </c>
       <c r="C16">
-        <v>110.3157885373775</v>
+        <v>106.255469017678</v>
       </c>
       <c r="D16">
-        <v>131.0937885373775</v>
+        <v>128.850469017678</v>
       </c>
       <c r="E16">
-        <v>-45.462</v>
+        <v>-43.645</v>
       </c>
       <c r="F16">
-        <v>25.438</v>
+        <v>27.255</v>
       </c>
       <c r="G16">
         <v>4.66</v>
@@ -2605,37 +2605,37 @@
         <v>2.5</v>
       </c>
       <c r="M16">
-        <v>5.998280400000001</v>
+        <v>6.426729000000001</v>
       </c>
       <c r="N16">
-        <v>-3.498280400000001</v>
+        <v>-3.926729000000001</v>
       </c>
       <c r="O16">
-        <v>-0.9795185120000003</v>
+        <v>-1.09948412</v>
       </c>
       <c r="P16">
-        <v>-2.518761888</v>
+        <v>-2.82724488</v>
       </c>
       <c r="Q16">
-        <v>14.981238112</v>
+        <v>14.67275512</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09432529297083238</v>
+        <v>0.09489617877048923</v>
       </c>
       <c r="T16">
-        <v>1.120676512028461</v>
+        <v>1.133860941581737</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.1167001129190293</v>
+        <v>0.108920105391094</v>
       </c>
       <c r="W16">
-        <v>0.2082821133736929</v>
+        <v>0.21011663914878</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.4167861175679616</v>
+        <v>0.3890003763967641</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1121792478272328</v>
+        <v>0.1140792478272329</v>
       </c>
       <c r="C17">
-        <v>106.255469017678</v>
+        <v>102.2706345979749</v>
       </c>
       <c r="D17">
-        <v>128.850469017678</v>
+        <v>126.6826345979749</v>
       </c>
       <c r="E17">
-        <v>-43.64500000000001</v>
+        <v>-41.828</v>
       </c>
       <c r="F17">
-        <v>27.255</v>
+        <v>29.072</v>
       </c>
       <c r="G17">
         <v>4.66</v>
@@ -2687,37 +2687,37 @@
         <v>2.5</v>
       </c>
       <c r="M17">
-        <v>6.426729</v>
+        <v>6.8551776</v>
       </c>
       <c r="N17">
-        <v>-3.926729</v>
+        <v>-4.3551776</v>
       </c>
       <c r="O17">
-        <v>-1.09948412</v>
+        <v>-1.219449728</v>
       </c>
       <c r="P17">
-        <v>-2.82724488</v>
+        <v>-3.135727872</v>
       </c>
       <c r="Q17">
-        <v>14.67275512</v>
+        <v>14.364272128</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09489617877048923</v>
+        <v>0.09548065708918554</v>
       </c>
       <c r="T17">
-        <v>1.133860941581737</v>
+        <v>1.147359286124377</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.108920105391094</v>
+        <v>0.1021125988041506</v>
       </c>
       <c r="W17">
-        <v>0.21011663914878</v>
+        <v>0.2117218492019813</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.3890003763967642</v>
+        <v>0.3646878528719665</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1140792478272329</v>
+        <v>0.1159792478272328</v>
       </c>
       <c r="C18">
-        <v>102.2706345979749</v>
+        <v>98.35753833924561</v>
       </c>
       <c r="D18">
-        <v>126.6826345979749</v>
+        <v>124.5865383392456</v>
       </c>
       <c r="E18">
-        <v>-41.828</v>
+        <v>-40.01100000000001</v>
       </c>
       <c r="F18">
-        <v>29.072</v>
+        <v>30.889</v>
       </c>
       <c r="G18">
         <v>4.66</v>
@@ -2769,37 +2769,37 @@
         <v>2.5</v>
       </c>
       <c r="M18">
-        <v>6.8551776</v>
+        <v>7.2836262</v>
       </c>
       <c r="N18">
-        <v>-4.3551776</v>
+        <v>-4.7836262</v>
       </c>
       <c r="O18">
-        <v>-1.219449728</v>
+        <v>-1.339415336</v>
       </c>
       <c r="P18">
-        <v>-3.135727872</v>
+        <v>-3.444210864</v>
       </c>
       <c r="Q18">
-        <v>14.364272128</v>
+        <v>14.055789136</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09548065708918554</v>
+        <v>0.09607921922279017</v>
       </c>
       <c r="T18">
-        <v>1.147359286124377</v>
+        <v>1.161182891981297</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.1021125988041506</v>
+        <v>0.09610597534508292</v>
       </c>
       <c r="W18">
-        <v>0.2117218492019813</v>
+        <v>0.2131382110136295</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.3646878528719665</v>
+        <v>0.343235626232439</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1159792478272328</v>
+        <v>0.1178792478272329</v>
       </c>
       <c r="C19">
-        <v>98.35753833924561</v>
+        <v>94.51267725408304</v>
       </c>
       <c r="D19">
-        <v>124.5865383392456</v>
+        <v>122.5586772540831</v>
       </c>
       <c r="E19">
-        <v>-40.01100000000001</v>
+        <v>-38.194</v>
       </c>
       <c r="F19">
-        <v>30.889</v>
+        <v>32.706</v>
       </c>
       <c r="G19">
         <v>4.66</v>
@@ -2851,37 +2851,37 @@
         <v>2.5</v>
       </c>
       <c r="M19">
-        <v>7.2836262</v>
+        <v>7.712074800000001</v>
       </c>
       <c r="N19">
-        <v>-4.7836262</v>
+        <v>-5.212074800000001</v>
       </c>
       <c r="O19">
-        <v>-1.339415336</v>
+        <v>-1.459380944</v>
       </c>
       <c r="P19">
-        <v>-3.444210864</v>
+        <v>-3.752693856</v>
       </c>
       <c r="Q19">
-        <v>14.055789136</v>
+        <v>13.747306144</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09607921922279017</v>
+        <v>0.0966923804328242</v>
       </c>
       <c r="T19">
-        <v>1.161182891981297</v>
+        <v>1.175343658956679</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.09610597534508292</v>
+        <v>0.09076675449257832</v>
       </c>
       <c r="W19">
-        <v>0.2131382110136295</v>
+        <v>0.21439719929065</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.343235626232439</v>
+        <v>0.3241669803306368</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1178792478272329</v>
+        <v>0.1197792478272328</v>
       </c>
       <c r="C20">
-        <v>94.51267725408306</v>
+        <v>90.73277277100387</v>
       </c>
       <c r="D20">
-        <v>122.5586772540831</v>
+        <v>120.5957727710039</v>
       </c>
       <c r="E20">
-        <v>-38.19400000000001</v>
+        <v>-36.37700000000001</v>
       </c>
       <c r="F20">
-        <v>32.706</v>
+        <v>34.523</v>
       </c>
       <c r="G20">
         <v>4.66</v>
@@ -2933,37 +2933,37 @@
         <v>2.5</v>
       </c>
       <c r="M20">
-        <v>7.712074799999999</v>
+        <v>8.140523399999999</v>
       </c>
       <c r="N20">
-        <v>-5.212074799999999</v>
+        <v>-5.640523399999999</v>
       </c>
       <c r="O20">
-        <v>-1.459380944</v>
+        <v>-1.579346552</v>
       </c>
       <c r="P20">
-        <v>-3.752693855999999</v>
+        <v>-4.061176848</v>
       </c>
       <c r="Q20">
-        <v>13.747306144</v>
+        <v>13.438823152</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0966923804328242</v>
+        <v>0.09732068142582202</v>
       </c>
       <c r="T20">
-        <v>1.175343658956679</v>
+        <v>1.189854074499354</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.09076675449257834</v>
+        <v>0.08598955688770579</v>
       </c>
       <c r="W20">
-        <v>0.21439719929065</v>
+        <v>0.215523662485879</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3241669803306368</v>
+        <v>0.3071055603132349</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1197792478272328</v>
+        <v>0.1216792478272329</v>
       </c>
       <c r="C21">
-        <v>90.73277277100387</v>
+        <v>87.0147530464692</v>
       </c>
       <c r="D21">
-        <v>120.5957727710039</v>
+        <v>118.6947530464692</v>
       </c>
       <c r="E21">
-        <v>-36.37700000000001</v>
+        <v>-34.56000000000001</v>
       </c>
       <c r="F21">
-        <v>34.523</v>
+        <v>36.34</v>
       </c>
       <c r="G21">
         <v>4.66</v>
@@ -3015,37 +3015,37 @@
         <v>2.5</v>
       </c>
       <c r="M21">
-        <v>8.140523399999999</v>
+        <v>8.568971999999999</v>
       </c>
       <c r="N21">
-        <v>-5.640523399999999</v>
+        <v>-6.068971999999999</v>
       </c>
       <c r="O21">
-        <v>-1.579346552</v>
+        <v>-1.69931216</v>
       </c>
       <c r="P21">
-        <v>-4.061176848</v>
+        <v>-4.369659839999999</v>
       </c>
       <c r="Q21">
-        <v>13.438823152</v>
+        <v>13.13034016</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09732068142582202</v>
+        <v>0.09796468994364479</v>
       </c>
       <c r="T21">
-        <v>1.189854074499354</v>
+        <v>1.204727250430596</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.08598955688770579</v>
+        <v>0.08169007904332051</v>
       </c>
       <c r="W21">
-        <v>0.215523662485879</v>
+        <v>0.216537479361585</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3071055603132349</v>
+        <v>0.2917502822975732</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1216792478272329</v>
+        <v>0.1235792478272329</v>
       </c>
       <c r="C22">
-        <v>87.0147530464692</v>
+        <v>83.35573692389741</v>
       </c>
       <c r="D22">
-        <v>118.6947530464692</v>
+        <v>116.8527369238974</v>
       </c>
       <c r="E22">
-        <v>-34.56000000000001</v>
+        <v>-32.743</v>
       </c>
       <c r="F22">
-        <v>36.34</v>
+        <v>38.157</v>
       </c>
       <c r="G22">
         <v>4.66</v>
@@ -3097,37 +3097,37 @@
         <v>2.5</v>
       </c>
       <c r="M22">
-        <v>8.568971999999999</v>
+        <v>8.997420600000002</v>
       </c>
       <c r="N22">
-        <v>-6.068971999999999</v>
+        <v>-6.497420600000002</v>
       </c>
       <c r="O22">
-        <v>-1.69931216</v>
+        <v>-1.819277768000001</v>
       </c>
       <c r="P22">
-        <v>-4.369659839999999</v>
+        <v>-4.678142832000001</v>
       </c>
       <c r="Q22">
-        <v>13.13034016</v>
+        <v>12.821857168</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09796468994364479</v>
+        <v>0.09862500247457701</v>
       </c>
       <c r="T22">
-        <v>1.204727250430596</v>
+        <v>1.219976962461363</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.08169007904332051</v>
+        <v>0.07780007527935283</v>
       </c>
       <c r="W22">
-        <v>0.216537479361585</v>
+        <v>0.2174547422491286</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.2917502822975732</v>
+        <v>0.2778574117119744</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1235792478272328</v>
+        <v>0.1254792478272329</v>
       </c>
       <c r="C23">
-        <v>83.35573692389742</v>
+        <v>79.75301936348563</v>
       </c>
       <c r="D23">
-        <v>116.8527369238974</v>
+        <v>115.0670193634856</v>
       </c>
       <c r="E23">
-        <v>-32.74300000000001</v>
+        <v>-30.92600000000001</v>
       </c>
       <c r="F23">
-        <v>38.157</v>
+        <v>39.974</v>
       </c>
       <c r="G23">
         <v>4.66</v>
@@ -3179,37 +3179,37 @@
         <v>2.5</v>
       </c>
       <c r="M23">
-        <v>8.9974206</v>
+        <v>9.425869199999999</v>
       </c>
       <c r="N23">
-        <v>-6.4974206</v>
+        <v>-6.925869199999999</v>
       </c>
       <c r="O23">
-        <v>-1.819277768</v>
+        <v>-1.939243376</v>
       </c>
       <c r="P23">
-        <v>-4.678142832</v>
+        <v>-4.986625823999999</v>
       </c>
       <c r="Q23">
-        <v>12.821857168</v>
+        <v>12.513374176</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09862500247457701</v>
+        <v>0.09930224609604596</v>
       </c>
       <c r="T23">
-        <v>1.219976962461363</v>
+        <v>1.235617692749329</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.07780007527935284</v>
+        <v>0.07426370822120046</v>
       </c>
       <c r="W23">
-        <v>0.2174547422491286</v>
+        <v>0.2182886176014409</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.2778574117119744</v>
+        <v>0.2652275293614301</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1254792478272329</v>
+        <v>0.1273792478272329</v>
       </c>
       <c r="C24">
-        <v>79.75301936348563</v>
+        <v>76.20405818787209</v>
       </c>
       <c r="D24">
-        <v>115.0670193634856</v>
+        <v>113.3350581878721</v>
       </c>
       <c r="E24">
-        <v>-30.92600000000001</v>
+        <v>-29.10900000000001</v>
       </c>
       <c r="F24">
-        <v>39.974</v>
+        <v>41.791</v>
       </c>
       <c r="G24">
         <v>4.66</v>
@@ -3261,37 +3261,37 @@
         <v>2.5</v>
       </c>
       <c r="M24">
-        <v>9.425869199999999</v>
+        <v>9.8543178</v>
       </c>
       <c r="N24">
-        <v>-6.925869199999999</v>
+        <v>-7.3543178</v>
       </c>
       <c r="O24">
-        <v>-1.939243376</v>
+        <v>-2.059208984000001</v>
       </c>
       <c r="P24">
-        <v>-4.986625823999999</v>
+        <v>-5.295108816</v>
       </c>
       <c r="Q24">
-        <v>12.513374176</v>
+        <v>12.204891184</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09930224609604596</v>
+        <v>0.09999708046092967</v>
       </c>
       <c r="T24">
-        <v>1.235617692749329</v>
+        <v>1.251664675772048</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.07426370822120046</v>
+        <v>0.07103485134201781</v>
       </c>
       <c r="W24">
-        <v>0.2182886176014409</v>
+        <v>0.2190499820535522</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2652275293614301</v>
+        <v>0.2536958976500636</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1273792478272329</v>
+        <v>0.1292792478272329</v>
       </c>
       <c r="C25">
-        <v>76.20405818787209</v>
+        <v>72.70646200705539</v>
       </c>
       <c r="D25">
-        <v>113.3350581878721</v>
+        <v>111.6544620070554</v>
       </c>
       <c r="E25">
-        <v>-29.10900000000001</v>
+        <v>-27.292</v>
       </c>
       <c r="F25">
-        <v>41.791</v>
+        <v>43.608</v>
       </c>
       <c r="G25">
         <v>4.66</v>
@@ -3343,37 +3343,37 @@
         <v>2.5</v>
       </c>
       <c r="M25">
-        <v>9.8543178</v>
+        <v>10.2827664</v>
       </c>
       <c r="N25">
-        <v>-7.3543178</v>
+        <v>-7.782766400000002</v>
       </c>
       <c r="O25">
-        <v>-2.059208984000001</v>
+        <v>-2.179174592000001</v>
       </c>
       <c r="P25">
-        <v>-5.295108816</v>
+        <v>-5.603591808000001</v>
       </c>
       <c r="Q25">
-        <v>12.204891184</v>
+        <v>11.896408192</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09999708046092967</v>
+        <v>0.1007101999406787</v>
       </c>
       <c r="T25">
-        <v>1.251664675772048</v>
+        <v>1.26813394782168</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.07103485134201781</v>
+        <v>0.06807506586943372</v>
       </c>
       <c r="W25">
-        <v>0.2190499820535522</v>
+        <v>0.2197478994679875</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2536958976500636</v>
+        <v>0.2431252352479776</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1292792478272329</v>
+        <v>0.1311792478272328</v>
       </c>
       <c r="C26">
-        <v>72.70646200705539</v>
+        <v>69.25797920195225</v>
       </c>
       <c r="D26">
-        <v>111.6544620070554</v>
+        <v>110.0229792019523</v>
       </c>
       <c r="E26">
-        <v>-27.29200000000001</v>
+        <v>-25.47500000000001</v>
       </c>
       <c r="F26">
-        <v>43.608</v>
+        <v>45.425</v>
       </c>
       <c r="G26">
         <v>4.66</v>
@@ -3425,37 +3425,37 @@
         <v>2.5</v>
       </c>
       <c r="M26">
-        <v>10.2827664</v>
+        <v>10.711215</v>
       </c>
       <c r="N26">
-        <v>-7.7827664</v>
+        <v>-8.211214999999999</v>
       </c>
       <c r="O26">
-        <v>-2.179174592</v>
+        <v>-2.2991402</v>
       </c>
       <c r="P26">
-        <v>-5.603591807999999</v>
+        <v>-5.912074799999999</v>
       </c>
       <c r="Q26">
-        <v>11.896408192</v>
+        <v>11.5879252</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1007101999406787</v>
+        <v>0.1014423359398878</v>
       </c>
       <c r="T26">
-        <v>1.26813394782168</v>
+        <v>1.285042400459302</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.06807506586943374</v>
+        <v>0.06535206323465639</v>
       </c>
       <c r="W26">
-        <v>0.2197478994679875</v>
+        <v>0.220389983489268</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2431252352479776</v>
+        <v>0.2334002258380585</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1311792478272328</v>
+        <v>0.1330792478272329</v>
       </c>
       <c r="C27">
-        <v>69.25797920195225</v>
+        <v>65.85648785987235</v>
       </c>
       <c r="D27">
-        <v>110.0229792019523</v>
+        <v>108.4384878598724</v>
       </c>
       <c r="E27">
-        <v>-25.47500000000001</v>
+        <v>-23.65800000000001</v>
       </c>
       <c r="F27">
-        <v>45.425</v>
+        <v>47.242</v>
       </c>
       <c r="G27">
         <v>4.66</v>
@@ -3507,37 +3507,37 @@
         <v>2.5</v>
       </c>
       <c r="M27">
-        <v>10.711215</v>
+        <v>11.1396636</v>
       </c>
       <c r="N27">
-        <v>-8.211214999999999</v>
+        <v>-8.6396636</v>
       </c>
       <c r="O27">
-        <v>-2.2991402</v>
+        <v>-2.419105808</v>
       </c>
       <c r="P27">
-        <v>-5.912074799999999</v>
+        <v>-6.220557792</v>
       </c>
       <c r="Q27">
-        <v>11.5879252</v>
+        <v>11.279442208</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1014423359398878</v>
+        <v>0.1021942593985349</v>
       </c>
       <c r="T27">
-        <v>1.285042400459302</v>
+        <v>1.302407838303347</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.06535206323465639</v>
+        <v>0.06283852234101577</v>
       </c>
       <c r="W27">
-        <v>0.220389983489268</v>
+        <v>0.2209826764319885</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2334002258380585</v>
+        <v>0.2244232940750562</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1330792478272329</v>
+        <v>0.1349792478272329</v>
       </c>
       <c r="C28">
-        <v>65.85648785987235</v>
+        <v>62.49998656730955</v>
       </c>
       <c r="D28">
-        <v>108.4384878598724</v>
+        <v>106.8989865673095</v>
       </c>
       <c r="E28">
-        <v>-23.65800000000001</v>
+        <v>-21.84100000000001</v>
       </c>
       <c r="F28">
-        <v>47.242</v>
+        <v>49.059</v>
       </c>
       <c r="G28">
         <v>4.66</v>
@@ -3589,37 +3589,37 @@
         <v>2.5</v>
       </c>
       <c r="M28">
-        <v>11.1396636</v>
+        <v>11.5681122</v>
       </c>
       <c r="N28">
-        <v>-8.6396636</v>
+        <v>-9.0681122</v>
       </c>
       <c r="O28">
-        <v>-2.419105808</v>
+        <v>-2.539071416</v>
       </c>
       <c r="P28">
-        <v>-6.220557792</v>
+        <v>-6.529040783999999</v>
       </c>
       <c r="Q28">
-        <v>11.279442208</v>
+        <v>10.970959216</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1021942593985349</v>
+        <v>0.1029667834998847</v>
       </c>
       <c r="T28">
-        <v>1.302407838303347</v>
+        <v>1.320249041567777</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.06283852234101577</v>
+        <v>0.06051116966171888</v>
       </c>
       <c r="W28">
-        <v>0.2209826764319885</v>
+        <v>0.2215314661937667</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2244232940750562</v>
+        <v>0.2161113202204246</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1349792478272329</v>
+        <v>0.1368792478272328</v>
       </c>
       <c r="C29">
-        <v>62.49998656730955</v>
+        <v>59.18658597604282</v>
       </c>
       <c r="D29">
-        <v>106.8989865673095</v>
+        <v>105.4025859760428</v>
       </c>
       <c r="E29">
-        <v>-21.84100000000001</v>
+        <v>-20.024</v>
       </c>
       <c r="F29">
-        <v>49.059</v>
+        <v>50.876</v>
       </c>
       <c r="G29">
         <v>4.66</v>
@@ -3671,37 +3671,37 @@
         <v>2.5</v>
       </c>
       <c r="M29">
-        <v>11.5681122</v>
+        <v>11.9965608</v>
       </c>
       <c r="N29">
-        <v>-9.0681122</v>
+        <v>-9.496560800000001</v>
       </c>
       <c r="O29">
-        <v>-2.539071416</v>
+        <v>-2.659037024000001</v>
       </c>
       <c r="P29">
-        <v>-6.529040783999999</v>
+        <v>-6.837523776</v>
       </c>
       <c r="Q29">
-        <v>10.970959216</v>
+        <v>10.662476224</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1029667834998847</v>
+        <v>0.1037607666040498</v>
       </c>
       <c r="T29">
-        <v>1.320249041567777</v>
+        <v>1.338585833811773</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.06051116966171888</v>
+        <v>0.05835005645951463</v>
       </c>
       <c r="W29">
-        <v>0.2215314661937667</v>
+        <v>0.2220410566868465</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2161113202204246</v>
+        <v>0.2083930587839808</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1368792478272328</v>
+        <v>0.1387792478272329</v>
       </c>
       <c r="C30">
-        <v>59.18658597604282</v>
+        <v>55.91450106781836</v>
       </c>
       <c r="D30">
-        <v>105.4025859760428</v>
+        <v>103.9475010678184</v>
       </c>
       <c r="E30">
-        <v>-20.024</v>
+        <v>-18.207</v>
       </c>
       <c r="F30">
-        <v>50.876</v>
+        <v>52.693</v>
       </c>
       <c r="G30">
         <v>4.66</v>
@@ -3753,37 +3753,37 @@
         <v>2.5</v>
       </c>
       <c r="M30">
-        <v>11.9965608</v>
+        <v>12.4250094</v>
       </c>
       <c r="N30">
-        <v>-9.496560800000001</v>
+        <v>-9.925009400000002</v>
       </c>
       <c r="O30">
-        <v>-2.659037024000001</v>
+        <v>-2.779002632000001</v>
       </c>
       <c r="P30">
-        <v>-6.837523776</v>
+        <v>-7.146006768000001</v>
       </c>
       <c r="Q30">
-        <v>10.662476224</v>
+        <v>10.353993232</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1037607666040498</v>
+        <v>0.1045771154294589</v>
       </c>
       <c r="T30">
-        <v>1.338585833811773</v>
+        <v>1.357439155414756</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.05835005645951463</v>
+        <v>0.05633798554711757</v>
       </c>
       <c r="W30">
-        <v>0.2220410566868465</v>
+        <v>0.2225155030079897</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2083930587839808</v>
+        <v>0.2012070912397056</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1387792478272328</v>
+        <v>0.1406792478272328</v>
       </c>
       <c r="C31">
-        <v>55.91450106781841</v>
+        <v>52.68204405102413</v>
       </c>
       <c r="D31">
-        <v>103.9475010678184</v>
+        <v>102.5320440510241</v>
       </c>
       <c r="E31">
-        <v>-18.20700000000001</v>
+        <v>-16.39000000000001</v>
       </c>
       <c r="F31">
-        <v>52.69299999999999</v>
+        <v>54.51</v>
       </c>
       <c r="G31">
         <v>4.66</v>
@@ -3835,37 +3835,37 @@
         <v>2.5</v>
       </c>
       <c r="M31">
-        <v>12.4250094</v>
+        <v>12.853458</v>
       </c>
       <c r="N31">
-        <v>-9.925009399999999</v>
+        <v>-10.353458</v>
       </c>
       <c r="O31">
-        <v>-2.779002632</v>
+        <v>-2.89896824</v>
       </c>
       <c r="P31">
-        <v>-7.146006767999999</v>
+        <v>-7.45448976</v>
       </c>
       <c r="Q31">
-        <v>10.353993232</v>
+        <v>10.04551024</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1045771154294589</v>
+        <v>0.1054167885070226</v>
       </c>
       <c r="T31">
-        <v>1.357439155414756</v>
+        <v>1.376831143349253</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.05633798554711759</v>
+        <v>0.054460052695547</v>
       </c>
       <c r="W31">
-        <v>0.2225155030079897</v>
+        <v>0.22295831957439</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2012070912397056</v>
+        <v>0.1945001881983821</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1406792478272328</v>
+        <v>0.1425792478272329</v>
       </c>
       <c r="C32">
-        <v>52.68204405102413</v>
+        <v>49.4876178299253</v>
       </c>
       <c r="D32">
-        <v>102.5320440510241</v>
+        <v>101.1546178299253</v>
       </c>
       <c r="E32">
-        <v>-16.39000000000001</v>
+        <v>-14.57300000000001</v>
       </c>
       <c r="F32">
-        <v>54.51</v>
+        <v>56.327</v>
       </c>
       <c r="G32">
         <v>4.66</v>
@@ -3917,37 +3917,37 @@
         <v>2.5</v>
       </c>
       <c r="M32">
-        <v>12.853458</v>
+        <v>13.2819066</v>
       </c>
       <c r="N32">
-        <v>-10.353458</v>
+        <v>-10.7819066</v>
       </c>
       <c r="O32">
-        <v>-2.89896824</v>
+        <v>-3.018933848</v>
       </c>
       <c r="P32">
-        <v>-7.45448976</v>
+        <v>-7.762972752</v>
       </c>
       <c r="Q32">
-        <v>10.04551024</v>
+        <v>9.737027248</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1054167885070226</v>
+        <v>0.1062807999346606</v>
       </c>
       <c r="T32">
-        <v>1.376831143349253</v>
+        <v>1.396785217890546</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.054460052695547</v>
+        <v>0.05270327680214226</v>
       </c>
       <c r="W32">
-        <v>0.22295831957439</v>
+        <v>0.2233725673300549</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1945001881983821</v>
+        <v>0.1882259885790795</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1425792478272329</v>
+        <v>0.1444792478272328</v>
       </c>
       <c r="C33">
-        <v>49.4876178299253</v>
+        <v>46.32970999333181</v>
       </c>
       <c r="D33">
-        <v>101.1546178299253</v>
+        <v>99.81370999333181</v>
       </c>
       <c r="E33">
-        <v>-14.57300000000001</v>
+        <v>-12.75600000000001</v>
       </c>
       <c r="F33">
-        <v>56.327</v>
+        <v>58.144</v>
       </c>
       <c r="G33">
         <v>4.66</v>
@@ -3999,37 +3999,37 @@
         <v>2.5</v>
       </c>
       <c r="M33">
-        <v>13.2819066</v>
+        <v>13.7103552</v>
       </c>
       <c r="N33">
-        <v>-10.7819066</v>
+        <v>-11.2103552</v>
       </c>
       <c r="O33">
-        <v>-3.018933848</v>
+        <v>-3.138899456</v>
       </c>
       <c r="P33">
-        <v>-7.762972752</v>
+        <v>-8.071455744</v>
       </c>
       <c r="Q33">
-        <v>9.737027248</v>
+        <v>9.428544256</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1062807999346606</v>
+        <v>0.1071702234631115</v>
       </c>
       <c r="T33">
-        <v>1.396785217890546</v>
+        <v>1.417326176977172</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.05270327680214226</v>
+        <v>0.0510562994020753</v>
       </c>
       <c r="W33">
-        <v>0.2233725673300549</v>
+        <v>0.2237609246009906</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1882259885790795</v>
+        <v>0.1823439264359832</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1444792478272328</v>
+        <v>0.1463792478272329</v>
       </c>
       <c r="C34">
-        <v>46.32970999333181</v>
+        <v>43.20688727512852</v>
       </c>
       <c r="D34">
-        <v>99.81370999333181</v>
+        <v>98.50788727512852</v>
       </c>
       <c r="E34">
-        <v>-12.75600000000001</v>
+        <v>-10.93900000000001</v>
       </c>
       <c r="F34">
-        <v>58.144</v>
+        <v>59.961</v>
       </c>
       <c r="G34">
         <v>4.66</v>
@@ -4081,37 +4081,37 @@
         <v>2.5</v>
       </c>
       <c r="M34">
-        <v>13.7103552</v>
+        <v>14.1388038</v>
       </c>
       <c r="N34">
-        <v>-11.2103552</v>
+        <v>-11.6388038</v>
       </c>
       <c r="O34">
-        <v>-3.138899456</v>
+        <v>-3.258865064</v>
       </c>
       <c r="P34">
-        <v>-8.071455744</v>
+        <v>-8.379938736</v>
       </c>
       <c r="Q34">
-        <v>9.428544256</v>
+        <v>9.120061264</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1071702234631115</v>
+        <v>0.1080861969476356</v>
       </c>
       <c r="T34">
-        <v>1.417326176977172</v>
+        <v>1.438480299021607</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.0510562994020753</v>
+        <v>0.04950913881413364</v>
       </c>
       <c r="W34">
-        <v>0.2237609246009906</v>
+        <v>0.2241257450676273</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1823439264359832</v>
+        <v>0.17681835290762</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1463792478272329</v>
+        <v>0.1482792478272328</v>
       </c>
       <c r="C35">
-        <v>43.20688727512852</v>
+        <v>40.11779044401454</v>
       </c>
       <c r="D35">
-        <v>98.50788727512852</v>
+        <v>97.23579044401454</v>
       </c>
       <c r="E35">
-        <v>-10.93900000000001</v>
+        <v>-9.122000000000007</v>
       </c>
       <c r="F35">
-        <v>59.961</v>
+        <v>61.778</v>
       </c>
       <c r="G35">
         <v>4.66</v>
@@ -4163,37 +4163,37 @@
         <v>2.5</v>
       </c>
       <c r="M35">
-        <v>14.1388038</v>
+        <v>14.5672524</v>
       </c>
       <c r="N35">
-        <v>-11.6388038</v>
+        <v>-12.0672524</v>
       </c>
       <c r="O35">
-        <v>-3.258865064</v>
+        <v>-3.378830672000001</v>
       </c>
       <c r="P35">
-        <v>-8.379938736</v>
+        <v>-8.688421728</v>
       </c>
       <c r="Q35">
-        <v>9.120061264</v>
+        <v>8.811578272</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1080861969476356</v>
+        <v>0.109029927204418</v>
       </c>
       <c r="T35">
-        <v>1.438480299021607</v>
+        <v>1.460275455067389</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.04950913881413364</v>
+        <v>0.04805298767254146</v>
       </c>
       <c r="W35">
-        <v>0.2241257450676273</v>
+        <v>0.2244691055068147</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.17681835290762</v>
+        <v>0.1716178131162195</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1482792478272328</v>
+        <v>0.1501792478272329</v>
       </c>
       <c r="C36">
-        <v>40.11779044401454</v>
+        <v>37.0611295841472</v>
       </c>
       <c r="D36">
-        <v>97.23579044401454</v>
+        <v>95.9961295841472</v>
       </c>
       <c r="E36">
-        <v>-9.122000000000007</v>
+        <v>-7.305000000000007</v>
       </c>
       <c r="F36">
-        <v>61.778</v>
+        <v>63.595</v>
       </c>
       <c r="G36">
         <v>4.66</v>
@@ -4245,37 +4245,37 @@
         <v>2.5</v>
       </c>
       <c r="M36">
-        <v>14.5672524</v>
+        <v>14.995701</v>
       </c>
       <c r="N36">
-        <v>-12.0672524</v>
+        <v>-12.495701</v>
       </c>
       <c r="O36">
-        <v>-3.378830672000001</v>
+        <v>-3.498796280000001</v>
       </c>
       <c r="P36">
-        <v>-8.688421728</v>
+        <v>-8.99690472</v>
       </c>
       <c r="Q36">
-        <v>8.811578272</v>
+        <v>8.50309528</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.109029927204418</v>
+        <v>0.1100026953152551</v>
       </c>
       <c r="T36">
-        <v>1.460275455067389</v>
+        <v>1.482741231299195</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.04805298767254146</v>
+        <v>0.04668004516761171</v>
       </c>
       <c r="W36">
-        <v>0.2244691055068147</v>
+        <v>0.2247928453494772</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1716178131162195</v>
+        <v>0.1667144470271846</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1501792478272329</v>
+        <v>0.1520792478272329</v>
       </c>
       <c r="C37">
-        <v>37.0611295841472</v>
+        <v>34.03567973224453</v>
       </c>
       <c r="D37">
-        <v>95.9961295841472</v>
+        <v>94.78767973224454</v>
       </c>
       <c r="E37">
-        <v>-7.305000000000007</v>
+        <v>-5.488</v>
       </c>
       <c r="F37">
-        <v>63.595</v>
+        <v>65.41200000000001</v>
       </c>
       <c r="G37">
         <v>4.66</v>
@@ -4327,37 +4327,37 @@
         <v>2.5</v>
       </c>
       <c r="M37">
-        <v>14.995701</v>
+        <v>15.4241496</v>
       </c>
       <c r="N37">
-        <v>-12.495701</v>
+        <v>-12.9241496</v>
       </c>
       <c r="O37">
-        <v>-3.498796280000001</v>
+        <v>-3.618761888000001</v>
       </c>
       <c r="P37">
-        <v>-8.99690472</v>
+        <v>-9.305387712000002</v>
       </c>
       <c r="Q37">
-        <v>8.50309528</v>
+        <v>8.194612287999998</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1100026953152551</v>
+        <v>0.111005862429556</v>
       </c>
       <c r="T37">
-        <v>1.482741231299195</v>
+        <v>1.505909063038245</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.04668004516761171</v>
+        <v>0.04538337724628916</v>
       </c>
       <c r="W37">
-        <v>0.2247928453494772</v>
+        <v>0.225098599645325</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1667144470271846</v>
+        <v>0.1620834901653184</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1520792478272328</v>
+        <v>0.1539792478272329</v>
       </c>
       <c r="C38">
-        <v>34.03567973224455</v>
+        <v>31.04027684012581</v>
       </c>
       <c r="D38">
-        <v>94.78767973224454</v>
+        <v>93.60927684012582</v>
       </c>
       <c r="E38">
-        <v>-5.488000000000014</v>
+        <v>-3.671000000000006</v>
       </c>
       <c r="F38">
-        <v>65.41199999999999</v>
+        <v>67.229</v>
       </c>
       <c r="G38">
         <v>4.66</v>
@@ -4409,37 +4409,37 @@
         <v>2.5</v>
       </c>
       <c r="M38">
-        <v>15.4241496</v>
+        <v>15.8525982</v>
       </c>
       <c r="N38">
-        <v>-12.9241496</v>
+        <v>-13.3525982</v>
       </c>
       <c r="O38">
-        <v>-3.618761888</v>
+        <v>-3.738727496000001</v>
       </c>
       <c r="P38">
-        <v>-9.305387711999998</v>
+        <v>-9.613870704</v>
       </c>
       <c r="Q38">
-        <v>8.194612288000002</v>
+        <v>7.886129296</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.111005862429556</v>
+        <v>0.112040876118914</v>
       </c>
       <c r="T38">
-        <v>1.505909063038245</v>
+        <v>1.52981238149917</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.04538337724628917</v>
+        <v>0.04415679948287594</v>
       </c>
       <c r="W38">
-        <v>0.225098599645325</v>
+        <v>0.2253878266819379</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1620834901653184</v>
+        <v>0.1577028552959855</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1539792478272329</v>
+        <v>0.1558792478272328</v>
       </c>
       <c r="C39">
-        <v>31.04027684012581</v>
+        <v>28.07381403471646</v>
       </c>
       <c r="D39">
-        <v>93.60927684012582</v>
+        <v>92.45981403471646</v>
       </c>
       <c r="E39">
-        <v>-3.671000000000006</v>
+        <v>-1.854000000000013</v>
       </c>
       <c r="F39">
-        <v>67.229</v>
+        <v>69.04599999999999</v>
       </c>
       <c r="G39">
         <v>4.66</v>
@@ -4491,37 +4491,37 @@
         <v>2.5</v>
       </c>
       <c r="M39">
-        <v>15.8525982</v>
+        <v>16.2810468</v>
       </c>
       <c r="N39">
-        <v>-13.3525982</v>
+        <v>-13.7810468</v>
       </c>
       <c r="O39">
-        <v>-3.738727496000001</v>
+        <v>-3.858693104</v>
       </c>
       <c r="P39">
-        <v>-9.613870704</v>
+        <v>-9.922353695999998</v>
       </c>
       <c r="Q39">
-        <v>7.886129296</v>
+        <v>7.577646304000002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.112040876118914</v>
+        <v>0.1131092773466384</v>
       </c>
       <c r="T39">
-        <v>1.52981238149917</v>
+        <v>1.554486774749156</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.04415679948287594</v>
+        <v>0.0429947784438529</v>
       </c>
       <c r="W39">
-        <v>0.2253878266819379</v>
+        <v>0.2256618312429395</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1577028552959855</v>
+        <v>0.1535527801566174</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1558792478272328</v>
+        <v>0.1577792478272328</v>
       </c>
       <c r="C40">
-        <v>28.07381403471646</v>
+        <v>25.13523815025944</v>
       </c>
       <c r="D40">
-        <v>92.45981403471646</v>
+        <v>91.33823815025944</v>
       </c>
       <c r="E40">
-        <v>-1.854000000000013</v>
+        <v>-0.03700000000000614</v>
       </c>
       <c r="F40">
-        <v>69.04599999999999</v>
+        <v>70.863</v>
       </c>
       <c r="G40">
         <v>4.66</v>
@@ -4573,37 +4573,37 @@
         <v>2.5</v>
       </c>
       <c r="M40">
-        <v>16.2810468</v>
+        <v>16.7094954</v>
       </c>
       <c r="N40">
-        <v>-13.7810468</v>
+        <v>-14.2094954</v>
       </c>
       <c r="O40">
-        <v>-3.858693104</v>
+        <v>-3.978658712000001</v>
       </c>
       <c r="P40">
-        <v>-9.922353695999998</v>
+        <v>-10.230836688</v>
       </c>
       <c r="Q40">
-        <v>7.577646304000002</v>
+        <v>7.269163312</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1131092773466384</v>
+        <v>0.1142127081228129</v>
       </c>
       <c r="T40">
-        <v>1.554486774749156</v>
+        <v>1.579970164499142</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.0429947784438529</v>
+        <v>0.04189234822734383</v>
       </c>
       <c r="W40">
-        <v>0.2256618312429395</v>
+        <v>0.2259217842879923</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1535527801566174</v>
+        <v>0.1496155293833709</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1577792478272328</v>
+        <v>0.1596792478272329</v>
       </c>
       <c r="C41">
-        <v>25.13523815025944</v>
+        <v>22.22354650989588</v>
       </c>
       <c r="D41">
-        <v>91.33823815025944</v>
+        <v>90.24354650989588</v>
       </c>
       <c r="E41">
-        <v>-0.03700000000000614</v>
+        <v>1.779999999999987</v>
       </c>
       <c r="F41">
-        <v>70.863</v>
+        <v>72.67999999999999</v>
       </c>
       <c r="G41">
         <v>4.66</v>
@@ -4655,37 +4655,37 @@
         <v>2.5</v>
       </c>
       <c r="M41">
-        <v>16.7094954</v>
+        <v>17.137944</v>
       </c>
       <c r="N41">
-        <v>-14.2094954</v>
+        <v>-14.637944</v>
       </c>
       <c r="O41">
-        <v>-3.978658712000001</v>
+        <v>-4.09862432</v>
       </c>
       <c r="P41">
-        <v>-10.230836688</v>
+        <v>-10.53931968</v>
       </c>
       <c r="Q41">
-        <v>7.269163312</v>
+        <v>6.960680320000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1142127081228129</v>
+        <v>0.1153529199248597</v>
       </c>
       <c r="T41">
-        <v>1.579970164499142</v>
+        <v>1.606303000574128</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.04189234822734383</v>
+        <v>0.04084503952166026</v>
       </c>
       <c r="W41">
-        <v>0.2259217842879923</v>
+        <v>0.2261687396807925</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1496155293833709</v>
+        <v>0.1458751411487866</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1596792478272329</v>
+        <v>0.1615792478272328</v>
       </c>
       <c r="C42">
-        <v>22.22354650989588</v>
+        <v>19.3377839359418</v>
       </c>
       <c r="D42">
-        <v>90.24354650989588</v>
+        <v>89.1747839359418</v>
       </c>
       <c r="E42">
-        <v>1.779999999999987</v>
+        <v>3.596999999999994</v>
       </c>
       <c r="F42">
-        <v>72.67999999999999</v>
+        <v>74.497</v>
       </c>
       <c r="G42">
         <v>4.66</v>
@@ -4737,37 +4737,37 @@
         <v>2.5</v>
       </c>
       <c r="M42">
-        <v>17.137944</v>
+        <v>17.5663926</v>
       </c>
       <c r="N42">
-        <v>-14.637944</v>
+        <v>-15.0663926</v>
       </c>
       <c r="O42">
-        <v>-4.09862432</v>
+        <v>-4.218589928</v>
       </c>
       <c r="P42">
-        <v>-10.53931968</v>
+        <v>-10.847802672</v>
       </c>
       <c r="Q42">
-        <v>6.960680320000002</v>
+        <v>6.652197328</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1153529199248597</v>
+        <v>0.1165317829744336</v>
       </c>
       <c r="T42">
-        <v>1.606303000574128</v>
+        <v>1.63352847516013</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.04084503952166026</v>
+        <v>0.03984881904552219</v>
       </c>
       <c r="W42">
-        <v>0.2261687396807925</v>
+        <v>0.2264036484690659</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1458751411487866</v>
+        <v>0.142317210876865</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1615792478272328</v>
+        <v>0.1634792478272329</v>
       </c>
       <c r="C43">
-        <v>19.3377839359418</v>
+        <v>16.47703997012378</v>
       </c>
       <c r="D43">
-        <v>89.1747839359418</v>
+        <v>88.13103997012379</v>
       </c>
       <c r="E43">
-        <v>3.596999999999994</v>
+        <v>5.414000000000001</v>
       </c>
       <c r="F43">
-        <v>74.497</v>
+        <v>76.31400000000001</v>
       </c>
       <c r="G43">
         <v>4.66</v>
@@ -4819,37 +4819,37 @@
         <v>2.5</v>
       </c>
       <c r="M43">
-        <v>17.5663926</v>
+        <v>17.9948412</v>
       </c>
       <c r="N43">
-        <v>-15.0663926</v>
+        <v>-15.4948412</v>
       </c>
       <c r="O43">
-        <v>-4.218589928</v>
+        <v>-4.338555536000001</v>
       </c>
       <c r="P43">
-        <v>-10.847802672</v>
+        <v>-11.156285664</v>
       </c>
       <c r="Q43">
-        <v>6.652197328</v>
+        <v>6.343714335999998</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1165317829744336</v>
+        <v>0.1177512964739929</v>
       </c>
       <c r="T43">
-        <v>1.63352847516013</v>
+        <v>1.661692759214615</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03984881904552219</v>
+        <v>0.03890003763967641</v>
       </c>
       <c r="W43">
-        <v>0.2264036484690659</v>
+        <v>0.2266273711245643</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.142317210876865</v>
+        <v>0.1389287058559872</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1634792478272328</v>
+        <v>0.1653792478272328</v>
       </c>
       <c r="C44">
-        <v>16.4770399701238</v>
+        <v>13.64044628677033</v>
       </c>
       <c r="D44">
-        <v>88.13103997012379</v>
+        <v>87.11144628677033</v>
       </c>
       <c r="E44">
-        <v>5.413999999999987</v>
+        <v>7.230999999999995</v>
       </c>
       <c r="F44">
-        <v>76.31399999999999</v>
+        <v>78.131</v>
       </c>
       <c r="G44">
         <v>4.66</v>
@@ -4901,37 +4901,37 @@
         <v>2.5</v>
       </c>
       <c r="M44">
-        <v>17.9948412</v>
+        <v>18.4232898</v>
       </c>
       <c r="N44">
-        <v>-15.4948412</v>
+        <v>-15.9232898</v>
       </c>
       <c r="O44">
-        <v>-4.338555536</v>
+        <v>-4.458521144000001</v>
       </c>
       <c r="P44">
-        <v>-11.156285664</v>
+        <v>-11.464768656</v>
       </c>
       <c r="Q44">
-        <v>6.343714336000001</v>
+        <v>6.035231344000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1177512964739928</v>
+        <v>0.119013599920905</v>
       </c>
       <c r="T44">
-        <v>1.661692759214615</v>
+        <v>1.69084526376224</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03890003763967642</v>
+        <v>0.03799538560154442</v>
       </c>
       <c r="W44">
-        <v>0.2266273711245643</v>
+        <v>0.2268406880751558</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1389287058559873</v>
+        <v>0.1356978057198015</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1653792478272328</v>
+        <v>0.1672792478272329</v>
       </c>
       <c r="C45">
-        <v>13.64044628677033</v>
+        <v>10.82717428351116</v>
       </c>
       <c r="D45">
-        <v>87.11144628677033</v>
+        <v>86.11517428351115</v>
       </c>
       <c r="E45">
-        <v>7.230999999999995</v>
+        <v>9.047999999999988</v>
       </c>
       <c r="F45">
-        <v>78.131</v>
+        <v>79.94799999999999</v>
       </c>
       <c r="G45">
         <v>4.66</v>
@@ -4983,37 +4983,37 @@
         <v>2.5</v>
       </c>
       <c r="M45">
-        <v>18.4232898</v>
+        <v>18.8517384</v>
       </c>
       <c r="N45">
-        <v>-15.9232898</v>
+        <v>-16.3517384</v>
       </c>
       <c r="O45">
-        <v>-4.458521144000001</v>
+        <v>-4.578486752</v>
       </c>
       <c r="P45">
-        <v>-11.464768656</v>
+        <v>-11.773251648</v>
       </c>
       <c r="Q45">
-        <v>6.035231344000001</v>
+        <v>5.726748352000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.119013599920905</v>
+        <v>0.1203209856337783</v>
       </c>
       <c r="T45">
-        <v>1.69084526376224</v>
+        <v>1.721038929186566</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03799538560154442</v>
+        <v>0.03713185411060023</v>
       </c>
       <c r="W45">
-        <v>0.2268406880751558</v>
+        <v>0.2270443088007205</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1356978057198015</v>
+        <v>0.1326137646807151</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1672792478272329</v>
+        <v>0.1691792478272329</v>
       </c>
       <c r="C46">
-        <v>10.82717428351116</v>
+        <v>8.036432835434667</v>
       </c>
       <c r="D46">
-        <v>86.11517428351115</v>
+        <v>85.14143283543467</v>
       </c>
       <c r="E46">
-        <v>9.047999999999988</v>
+        <v>10.86499999999999</v>
       </c>
       <c r="F46">
-        <v>79.94799999999999</v>
+        <v>81.765</v>
       </c>
       <c r="G46">
         <v>4.66</v>
@@ -5065,37 +5065,37 @@
         <v>2.5</v>
       </c>
       <c r="M46">
-        <v>18.8517384</v>
+        <v>19.280187</v>
       </c>
       <c r="N46">
-        <v>-16.3517384</v>
+        <v>-16.780187</v>
       </c>
       <c r="O46">
-        <v>-4.578486752</v>
+        <v>-4.698452360000001</v>
       </c>
       <c r="P46">
-        <v>-11.773251648</v>
+        <v>-12.08173464</v>
       </c>
       <c r="Q46">
-        <v>5.726748352000001</v>
+        <v>5.418265359999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1203209856337783</v>
+        <v>0.1216759126453015</v>
       </c>
       <c r="T46">
-        <v>1.721038929186566</v>
+        <v>1.752330546080867</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03713185411060023</v>
+        <v>0.03630670179703132</v>
       </c>
       <c r="W46">
-        <v>0.2270443088007205</v>
+        <v>0.22723887971626</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1326137646807151</v>
+        <v>0.1296667921322547</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1691792478272329</v>
+        <v>0.1710792478272329</v>
       </c>
       <c r="C47">
-        <v>8.036432835434667</v>
+        <v>5.267466199910118</v>
       </c>
       <c r="D47">
-        <v>85.14143283543467</v>
+        <v>84.18946619991011</v>
       </c>
       <c r="E47">
-        <v>10.86499999999999</v>
+        <v>12.68199999999999</v>
       </c>
       <c r="F47">
-        <v>81.765</v>
+        <v>83.58199999999999</v>
       </c>
       <c r="G47">
         <v>4.66</v>
@@ -5147,37 +5147,37 @@
         <v>2.5</v>
       </c>
       <c r="M47">
-        <v>19.280187</v>
+        <v>19.7086356</v>
       </c>
       <c r="N47">
-        <v>-16.780187</v>
+        <v>-17.2086356</v>
       </c>
       <c r="O47">
-        <v>-4.698452360000001</v>
+        <v>-4.818417968</v>
       </c>
       <c r="P47">
-        <v>-12.08173464</v>
+        <v>-12.390217632</v>
       </c>
       <c r="Q47">
-        <v>5.418265359999999</v>
+        <v>5.109782367999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1216759126453015</v>
+        <v>0.123081022138733</v>
       </c>
       <c r="T47">
-        <v>1.752330546080867</v>
+        <v>1.784781111749031</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03630670179703132</v>
+        <v>0.03551742567100891</v>
       </c>
       <c r="W47">
-        <v>0.22723887971626</v>
+        <v>0.2274249910267761</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1296667921322547</v>
+        <v>0.1268479488250318</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1710792478272329</v>
+        <v>0.1729792478272328</v>
       </c>
       <c r="C48">
-        <v>5.267466199910118</v>
+        <v>2.519552060412465</v>
       </c>
       <c r="D48">
-        <v>84.18946619991011</v>
+        <v>83.25855206041247</v>
       </c>
       <c r="E48">
-        <v>12.68199999999999</v>
+        <v>14.499</v>
       </c>
       <c r="F48">
-        <v>83.58199999999999</v>
+        <v>85.399</v>
       </c>
       <c r="G48">
         <v>4.66</v>
@@ -5229,37 +5229,37 @@
         <v>2.5</v>
       </c>
       <c r="M48">
-        <v>19.7086356</v>
+        <v>20.1370842</v>
       </c>
       <c r="N48">
-        <v>-17.2086356</v>
+        <v>-17.6370842</v>
       </c>
       <c r="O48">
-        <v>-4.818417968</v>
+        <v>-4.938383576000001</v>
       </c>
       <c r="P48">
-        <v>-12.390217632</v>
+        <v>-12.698700624</v>
       </c>
       <c r="Q48">
-        <v>5.109782367999999</v>
+        <v>4.801299375999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.123081022138733</v>
+        <v>0.1245391546319167</v>
       </c>
       <c r="T48">
-        <v>1.784781111749031</v>
+        <v>1.81845622706505</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03551742567100891</v>
+        <v>0.0347617357631151</v>
       </c>
       <c r="W48">
-        <v>0.2274249910267761</v>
+        <v>0.2276031827070575</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1268479488250318</v>
+        <v>0.1241490562968396</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1729792478272328</v>
+        <v>0.1748792478272329</v>
       </c>
       <c r="C49">
-        <v>2.519552060412465</v>
+        <v>-0.2080003012909799</v>
       </c>
       <c r="D49">
-        <v>83.25855206041247</v>
+        <v>82.34799969870903</v>
       </c>
       <c r="E49">
-        <v>14.499</v>
+        <v>16.316</v>
       </c>
       <c r="F49">
-        <v>85.399</v>
+        <v>87.21600000000001</v>
       </c>
       <c r="G49">
         <v>4.66</v>
@@ -5311,37 +5311,37 @@
         <v>2.5</v>
       </c>
       <c r="M49">
-        <v>20.1370842</v>
+        <v>20.5655328</v>
       </c>
       <c r="N49">
-        <v>-17.6370842</v>
+        <v>-18.0655328</v>
       </c>
       <c r="O49">
-        <v>-4.938383576000001</v>
+        <v>-5.058349184000002</v>
       </c>
       <c r="P49">
-        <v>-12.698700624</v>
+        <v>-13.007183616</v>
       </c>
       <c r="Q49">
-        <v>4.801299375999999</v>
+        <v>4.492816383999997</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1245391546319167</v>
+        <v>0.1260533691440689</v>
       </c>
       <c r="T49">
-        <v>1.81845622706505</v>
+        <v>1.853426539123994</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0347617357631151</v>
+        <v>0.03403753293471686</v>
       </c>
       <c r="W49">
-        <v>0.2276031827070575</v>
+        <v>0.2277739497339938</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1241490562968396</v>
+        <v>0.1215626176239888</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1748792478272329</v>
+        <v>0.1767792478272328</v>
       </c>
       <c r="C50">
-        <v>-0.2080003012909657</v>
+        <v>-2.915851714312637</v>
       </c>
       <c r="D50">
-        <v>82.34799969870903</v>
+        <v>81.45714828568735</v>
       </c>
       <c r="E50">
-        <v>16.31599999999999</v>
+        <v>18.13299999999998</v>
       </c>
       <c r="F50">
-        <v>87.21599999999999</v>
+        <v>89.03299999999999</v>
       </c>
       <c r="G50">
         <v>4.66</v>
@@ -5393,37 +5393,37 @@
         <v>2.5</v>
       </c>
       <c r="M50">
-        <v>20.5655328</v>
+        <v>20.9939814</v>
       </c>
       <c r="N50">
-        <v>-18.0655328</v>
+        <v>-18.4939814</v>
       </c>
       <c r="O50">
-        <v>-5.058349184000001</v>
+        <v>-5.178314792</v>
       </c>
       <c r="P50">
-        <v>-13.007183616</v>
+        <v>-13.315666608</v>
       </c>
       <c r="Q50">
-        <v>4.492816384000001</v>
+        <v>4.184333392000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1260533691440689</v>
+        <v>0.127626964617482</v>
       </c>
       <c r="T50">
-        <v>1.853426539123994</v>
+        <v>1.889768235969562</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03403753293471687</v>
+        <v>0.03334288940543693</v>
       </c>
       <c r="W50">
-        <v>0.2277739497339938</v>
+        <v>0.227937746678198</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1215626176239888</v>
+        <v>0.1190817478765605</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1767792478272328</v>
+        <v>0.1786792478272329</v>
       </c>
       <c r="C51">
-        <v>-2.915851714312637</v>
+        <v>-5.604634718064304</v>
       </c>
       <c r="D51">
-        <v>81.45714828568735</v>
+        <v>80.58536528193569</v>
       </c>
       <c r="E51">
-        <v>18.13299999999998</v>
+        <v>19.94999999999999</v>
       </c>
       <c r="F51">
-        <v>89.03299999999999</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="G51">
         <v>4.66</v>
@@ -5475,37 +5475,37 @@
         <v>2.5</v>
       </c>
       <c r="M51">
-        <v>20.9939814</v>
+        <v>21.42243</v>
       </c>
       <c r="N51">
-        <v>-18.4939814</v>
+        <v>-18.92243</v>
       </c>
       <c r="O51">
-        <v>-5.178314792</v>
+        <v>-5.2982804</v>
       </c>
       <c r="P51">
-        <v>-13.315666608</v>
+        <v>-13.6241496</v>
       </c>
       <c r="Q51">
-        <v>4.184333392000001</v>
+        <v>3.875850400000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.127626964617482</v>
+        <v>0.1292635039098317</v>
       </c>
       <c r="T51">
-        <v>1.889768235969562</v>
+        <v>1.927563600688954</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03334288940543693</v>
+        <v>0.0326760316173282</v>
       </c>
       <c r="W51">
-        <v>0.227937746678198</v>
+        <v>0.228094991744634</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1190817478765605</v>
+        <v>0.1167001129190293</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1786792478272329</v>
+        <v>0.1805792478272329</v>
       </c>
       <c r="C52">
-        <v>-5.604634718064304</v>
+        <v>-8.274955060058389</v>
       </c>
       <c r="D52">
-        <v>80.58536528193569</v>
+        <v>79.73204493994162</v>
       </c>
       <c r="E52">
-        <v>19.94999999999999</v>
+        <v>21.767</v>
       </c>
       <c r="F52">
-        <v>90.84999999999999</v>
+        <v>92.667</v>
       </c>
       <c r="G52">
         <v>4.66</v>
@@ -5557,37 +5557,37 @@
         <v>2.5</v>
       </c>
       <c r="M52">
-        <v>21.42243</v>
+        <v>21.8508786</v>
       </c>
       <c r="N52">
-        <v>-18.92243</v>
+        <v>-19.3508786</v>
       </c>
       <c r="O52">
-        <v>-5.2982804</v>
+        <v>-5.418246008000001</v>
       </c>
       <c r="P52">
-        <v>-13.6241496</v>
+        <v>-13.932632592</v>
       </c>
       <c r="Q52">
-        <v>3.875850400000001</v>
+        <v>3.567367407999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1292635039098317</v>
+        <v>0.1309668407243181</v>
       </c>
       <c r="T52">
-        <v>1.927563600688954</v>
+        <v>1.966901633356075</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0326760316173282</v>
+        <v>0.03203532511502764</v>
       </c>
       <c r="W52">
-        <v>0.228094991744634</v>
+        <v>0.2282460703378765</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1167001129190293</v>
+        <v>0.114411875410813</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1805792478272329</v>
+        <v>0.1824792478272328</v>
       </c>
       <c r="C53">
-        <v>-8.274955060058389</v>
+        <v>-10.92739309954517</v>
       </c>
       <c r="D53">
-        <v>79.73204493994162</v>
+        <v>78.89660690045483</v>
       </c>
       <c r="E53">
-        <v>21.767</v>
+        <v>23.58399999999999</v>
       </c>
       <c r="F53">
-        <v>92.667</v>
+        <v>94.48399999999999</v>
       </c>
       <c r="G53">
         <v>4.66</v>
@@ -5639,37 +5639,37 @@
         <v>2.5</v>
       </c>
       <c r="M53">
-        <v>21.8508786</v>
+        <v>22.2793272</v>
       </c>
       <c r="N53">
-        <v>-19.3508786</v>
+        <v>-19.7793272</v>
       </c>
       <c r="O53">
-        <v>-5.418246008000001</v>
+        <v>-5.538211616000001</v>
       </c>
       <c r="P53">
-        <v>-13.932632592</v>
+        <v>-14.241115584</v>
       </c>
       <c r="Q53">
-        <v>3.567367407999999</v>
+        <v>3.258884416000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1309668407243181</v>
+        <v>0.1327411499060747</v>
       </c>
       <c r="T53">
-        <v>1.966901633356075</v>
+        <v>2.00787875071766</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03203532511502764</v>
+        <v>0.03141926117050788</v>
       </c>
       <c r="W53">
-        <v>0.2282460703378765</v>
+        <v>0.2283913382159942</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.114411875410813</v>
+        <v>0.1122116470375282</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1824792478272328</v>
+        <v>0.1843792478272329</v>
       </c>
       <c r="C54">
-        <v>-10.92739309954517</v>
+        <v>-13.56250512382061</v>
       </c>
       <c r="D54">
-        <v>78.89660690045483</v>
+        <v>78.07849487617939</v>
       </c>
       <c r="E54">
-        <v>23.58399999999999</v>
+        <v>25.401</v>
       </c>
       <c r="F54">
-        <v>94.48399999999999</v>
+        <v>96.301</v>
       </c>
       <c r="G54">
         <v>4.66</v>
@@ -5721,37 +5721,37 @@
         <v>2.5</v>
       </c>
       <c r="M54">
-        <v>22.2793272</v>
+        <v>22.7077758</v>
       </c>
       <c r="N54">
-        <v>-19.7793272</v>
+        <v>-20.2077758</v>
       </c>
       <c r="O54">
-        <v>-5.538211616000001</v>
+        <v>-5.658177224000001</v>
       </c>
       <c r="P54">
-        <v>-14.241115584</v>
+        <v>-14.549598576</v>
       </c>
       <c r="Q54">
-        <v>3.258884416000001</v>
+        <v>2.950401424000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1327411499060747</v>
+        <v>0.1345909616062039</v>
       </c>
       <c r="T54">
-        <v>2.00787875071766</v>
+        <v>2.050599575201014</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03141926117050788</v>
+        <v>0.03082644492200773</v>
       </c>
       <c r="W54">
-        <v>0.2283913382159942</v>
+        <v>0.2285311242873906</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1122116470375282</v>
+        <v>0.1100944461500276</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1843792478272329</v>
+        <v>0.1862792478272329</v>
       </c>
       <c r="C55">
-        <v>-13.56250512382061</v>
+        <v>-16.18082458347833</v>
       </c>
       <c r="D55">
-        <v>78.07849487617939</v>
+        <v>77.27717541652167</v>
       </c>
       <c r="E55">
-        <v>25.401</v>
+        <v>27.21799999999999</v>
       </c>
       <c r="F55">
-        <v>96.301</v>
+        <v>98.11799999999999</v>
       </c>
       <c r="G55">
         <v>4.66</v>
@@ -5803,37 +5803,37 @@
         <v>2.5</v>
       </c>
       <c r="M55">
-        <v>22.7077758</v>
+        <v>23.1362244</v>
       </c>
       <c r="N55">
-        <v>-20.2077758</v>
+        <v>-20.6362244</v>
       </c>
       <c r="O55">
-        <v>-5.658177224000001</v>
+        <v>-5.778142832</v>
       </c>
       <c r="P55">
-        <v>-14.549598576</v>
+        <v>-14.858081568</v>
       </c>
       <c r="Q55">
-        <v>2.950401424000001</v>
+        <v>2.641918432000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1345909616062039</v>
+        <v>0.136521199901991</v>
       </c>
       <c r="T55">
-        <v>2.050599575201014</v>
+        <v>2.095177826835819</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03082644492200773</v>
+        <v>0.03025558483085944</v>
       </c>
       <c r="W55">
-        <v>0.2285311242873906</v>
+        <v>0.2286657330968833</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1100944461500276</v>
+        <v>0.1080556601102123</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1862792478272329</v>
+        <v>0.1881792478272329</v>
       </c>
       <c r="C56">
-        <v>-16.18082458347833</v>
+        <v>-18.78286325237013</v>
       </c>
       <c r="D56">
-        <v>77.27717541652167</v>
+        <v>76.49213674762987</v>
       </c>
       <c r="E56">
-        <v>27.21799999999999</v>
+        <v>29.035</v>
       </c>
       <c r="F56">
-        <v>98.11799999999999</v>
+        <v>99.935</v>
       </c>
       <c r="G56">
         <v>4.66</v>
@@ -5885,37 +5885,37 @@
         <v>2.5</v>
       </c>
       <c r="M56">
-        <v>23.1362244</v>
+        <v>23.564673</v>
       </c>
       <c r="N56">
-        <v>-20.6362244</v>
+        <v>-21.064673</v>
       </c>
       <c r="O56">
-        <v>-5.778142832</v>
+        <v>-5.898108440000001</v>
       </c>
       <c r="P56">
-        <v>-14.858081568</v>
+        <v>-15.16656456</v>
       </c>
       <c r="Q56">
-        <v>2.641918432000001</v>
+        <v>2.333435439999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.136521199901991</v>
+        <v>0.1385372265664797</v>
       </c>
       <c r="T56">
-        <v>2.095177826835819</v>
+        <v>2.141737334098838</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03025558483085944</v>
+        <v>0.02970548328848018</v>
       </c>
       <c r="W56">
-        <v>0.2286657330968833</v>
+        <v>0.2287954470405764</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1080556601102123</v>
+        <v>0.106091011744572</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1881792478272329</v>
+        <v>0.1900792478272328</v>
       </c>
       <c r="C57">
-        <v>-18.78286325237013</v>
+        <v>-21.36911231757533</v>
       </c>
       <c r="D57">
-        <v>76.49213674762987</v>
+        <v>75.72288768242468</v>
       </c>
       <c r="E57">
-        <v>29.035</v>
+        <v>30.852</v>
       </c>
       <c r="F57">
-        <v>99.935</v>
+        <v>101.752</v>
       </c>
       <c r="G57">
         <v>4.66</v>
@@ -5967,37 +5967,37 @@
         <v>2.5</v>
       </c>
       <c r="M57">
-        <v>23.564673</v>
+        <v>23.9931216</v>
       </c>
       <c r="N57">
-        <v>-21.064673</v>
+        <v>-21.4931216</v>
       </c>
       <c r="O57">
-        <v>-5.898108440000001</v>
+        <v>-6.018074048000001</v>
       </c>
       <c r="P57">
-        <v>-15.16656456</v>
+        <v>-15.475047552</v>
       </c>
       <c r="Q57">
-        <v>2.333435439999999</v>
+        <v>2.024952447999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1385372265664797</v>
+        <v>0.1406448908066269</v>
       </c>
       <c r="T57">
-        <v>2.141737334098838</v>
+        <v>2.190413182601084</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02970548328848018</v>
+        <v>0.02917502822975732</v>
       </c>
       <c r="W57">
-        <v>0.2287954470405764</v>
+        <v>0.2289205283434232</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.106091011744572</v>
+        <v>0.1041965293919904</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1900792478272328</v>
+        <v>0.1919792478272329</v>
       </c>
       <c r="C58">
-        <v>-21.36911231757533</v>
+        <v>-23.94004340425622</v>
       </c>
       <c r="D58">
-        <v>75.72288768242468</v>
+        <v>74.96895659574379</v>
       </c>
       <c r="E58">
-        <v>30.852</v>
+        <v>32.669</v>
       </c>
       <c r="F58">
-        <v>101.752</v>
+        <v>103.569</v>
       </c>
       <c r="G58">
         <v>4.66</v>
@@ -6049,37 +6049,37 @@
         <v>2.5</v>
       </c>
       <c r="M58">
-        <v>23.9931216</v>
+        <v>24.4215702</v>
       </c>
       <c r="N58">
-        <v>-21.4931216</v>
+        <v>-21.9215702</v>
       </c>
       <c r="O58">
-        <v>-6.018074048000001</v>
+        <v>-6.138039656000001</v>
       </c>
       <c r="P58">
-        <v>-15.475047552</v>
+        <v>-15.783530544</v>
       </c>
       <c r="Q58">
-        <v>2.024952447999999</v>
+        <v>1.716469455999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1406448908066269</v>
+        <v>0.1428505859416647</v>
       </c>
       <c r="T58">
-        <v>2.190413182601084</v>
+        <v>2.241353024056923</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02917502822975732</v>
+        <v>0.02866318562923526</v>
       </c>
       <c r="W58">
-        <v>0.2289205283434232</v>
+        <v>0.2290412208286263</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1041965293919904</v>
+        <v>0.1023685201044117</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1919792478272329</v>
+        <v>0.1938792478272329</v>
       </c>
       <c r="C59">
-        <v>-23.94004340425622</v>
+        <v>-26.49610953989411</v>
       </c>
       <c r="D59">
-        <v>74.96895659574379</v>
+        <v>74.22989046010591</v>
       </c>
       <c r="E59">
-        <v>32.669</v>
+        <v>34.486</v>
       </c>
       <c r="F59">
-        <v>103.569</v>
+        <v>105.386</v>
       </c>
       <c r="G59">
         <v>4.66</v>
@@ -6131,37 +6131,37 @@
         <v>2.5</v>
       </c>
       <c r="M59">
-        <v>24.4215702</v>
+        <v>24.8500188</v>
       </c>
       <c r="N59">
-        <v>-21.9215702</v>
+        <v>-22.3500188</v>
       </c>
       <c r="O59">
-        <v>-6.138039656000001</v>
+        <v>-6.258005264000002</v>
       </c>
       <c r="P59">
-        <v>-15.783530544</v>
+        <v>-16.092013536</v>
       </c>
       <c r="Q59">
-        <v>1.716469455999999</v>
+        <v>1.407986463999997</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1428505859416647</v>
+        <v>0.1451613141783711</v>
       </c>
       <c r="T59">
-        <v>2.241353024056923</v>
+        <v>2.294718572248755</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02866318562923526</v>
+        <v>0.02816899277355879</v>
       </c>
       <c r="W59">
-        <v>0.2290412208286263</v>
+        <v>0.2291577515039948</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1023685201044117</v>
+        <v>0.1006035456198527</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1938792478272328</v>
+        <v>0.1957792478272329</v>
       </c>
       <c r="C60">
-        <v>-26.49610953989408</v>
+        <v>-29.0377460620474</v>
       </c>
       <c r="D60">
-        <v>74.22989046010591</v>
+        <v>73.50525393795259</v>
       </c>
       <c r="E60">
-        <v>34.48599999999998</v>
+        <v>36.30299999999998</v>
       </c>
       <c r="F60">
-        <v>105.386</v>
+        <v>107.203</v>
       </c>
       <c r="G60">
         <v>4.66</v>
@@ -6213,37 +6213,37 @@
         <v>2.5</v>
       </c>
       <c r="M60">
-        <v>24.8500188</v>
+        <v>25.2784674</v>
       </c>
       <c r="N60">
-        <v>-22.3500188</v>
+        <v>-22.7784674</v>
       </c>
       <c r="O60">
-        <v>-6.258005263999999</v>
+        <v>-6.377970872</v>
       </c>
       <c r="P60">
-        <v>-16.092013536</v>
+        <v>-16.400496528</v>
       </c>
       <c r="Q60">
-        <v>1.407986464000004</v>
+        <v>1.099503472000002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1451613141783711</v>
+        <v>0.1475847608656484</v>
       </c>
       <c r="T60">
-        <v>2.294718572248754</v>
+        <v>2.350687317913358</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02816899277355879</v>
+        <v>0.02769155221807474</v>
       </c>
       <c r="W60">
-        <v>0.2291577515039948</v>
+        <v>0.229270331986978</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1006035456198529</v>
+        <v>0.09889840077883838</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1957792478272329</v>
+        <v>0.1976792478272328</v>
       </c>
       <c r="C61">
-        <v>-29.0377460620474</v>
+        <v>-31.56537147345456</v>
       </c>
       <c r="D61">
-        <v>73.50525393795259</v>
+        <v>72.79462852654544</v>
       </c>
       <c r="E61">
-        <v>36.30299999999998</v>
+        <v>38.11999999999999</v>
       </c>
       <c r="F61">
-        <v>107.203</v>
+        <v>109.02</v>
       </c>
       <c r="G61">
         <v>4.66</v>
@@ -6295,37 +6295,37 @@
         <v>2.5</v>
       </c>
       <c r="M61">
-        <v>25.2784674</v>
+        <v>25.706916</v>
       </c>
       <c r="N61">
-        <v>-22.7784674</v>
+        <v>-23.206916</v>
       </c>
       <c r="O61">
-        <v>-6.377970872</v>
+        <v>-6.497936480000001</v>
       </c>
       <c r="P61">
-        <v>-16.400496528</v>
+        <v>-16.70897952</v>
       </c>
       <c r="Q61">
-        <v>1.099503472000002</v>
+        <v>0.7910204800000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1475847608656484</v>
+        <v>0.1501293798872896</v>
       </c>
       <c r="T61">
-        <v>2.350687317913358</v>
+        <v>2.409454500861191</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02769155221807474</v>
+        <v>0.0272300263477735</v>
       </c>
       <c r="W61">
-        <v>0.229270331986978</v>
+        <v>0.229379159787195</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.09889840077883838</v>
+        <v>0.09725009409919105</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1976792478272328</v>
+        <v>0.1995792478272329</v>
       </c>
       <c r="C62">
-        <v>-31.56537147345456</v>
+        <v>-34.07938824801026</v>
       </c>
       <c r="D62">
-        <v>72.79462852654544</v>
+        <v>72.09761175198973</v>
       </c>
       <c r="E62">
-        <v>38.11999999999999</v>
+        <v>39.93699999999998</v>
       </c>
       <c r="F62">
-        <v>109.02</v>
+        <v>110.837</v>
       </c>
       <c r="G62">
         <v>4.66</v>
@@ -6377,37 +6377,37 @@
         <v>2.5</v>
       </c>
       <c r="M62">
-        <v>25.706916</v>
+        <v>26.1353646</v>
       </c>
       <c r="N62">
-        <v>-23.206916</v>
+        <v>-23.6353646</v>
       </c>
       <c r="O62">
-        <v>-6.497936480000001</v>
+        <v>-6.617902088</v>
       </c>
       <c r="P62">
-        <v>-16.70897952</v>
+        <v>-17.017462512</v>
       </c>
       <c r="Q62">
-        <v>0.7910204800000002</v>
+        <v>0.482537488000002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1501293798872896</v>
+        <v>0.1528044921920919</v>
       </c>
       <c r="T62">
-        <v>2.409454500861191</v>
+        <v>2.471235385498658</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0272300263477735</v>
+        <v>0.02678363247321984</v>
       </c>
       <c r="W62">
-        <v>0.229379159787195</v>
+        <v>0.2294844194628148</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.09725009409919105</v>
+        <v>0.09565583026149937</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1995792478272329</v>
+        <v>0.2014792478272329</v>
       </c>
       <c r="C63">
-        <v>-34.07938824801026</v>
+        <v>-36.58018359087748</v>
       </c>
       <c r="D63">
-        <v>72.09761175198973</v>
+        <v>71.41381640912252</v>
       </c>
       <c r="E63">
-        <v>39.93699999999998</v>
+        <v>41.75399999999999</v>
       </c>
       <c r="F63">
-        <v>110.837</v>
+        <v>112.654</v>
       </c>
       <c r="G63">
         <v>4.66</v>
@@ -6459,37 +6459,37 @@
         <v>2.5</v>
       </c>
       <c r="M63">
-        <v>26.1353646</v>
+        <v>26.5638132</v>
       </c>
       <c r="N63">
-        <v>-23.6353646</v>
+        <v>-24.0638132</v>
       </c>
       <c r="O63">
-        <v>-6.617902088</v>
+        <v>-6.737867696</v>
       </c>
       <c r="P63">
-        <v>-17.017462512</v>
+        <v>-17.325945504</v>
       </c>
       <c r="Q63">
-        <v>0.482537488000002</v>
+        <v>0.1740544960000037</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1528044921920919</v>
+        <v>0.1556203998813575</v>
       </c>
       <c r="T63">
-        <v>2.471235385498658</v>
+        <v>2.53626789564336</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02678363247321984</v>
+        <v>0.02635163840107113</v>
       </c>
       <c r="W63">
-        <v>0.2294844194628148</v>
+        <v>0.2295862836650274</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.09565583026149937</v>
+        <v>0.09411299428953979</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2014792478272329</v>
+        <v>0.2033792478272329</v>
       </c>
       <c r="C64">
-        <v>-36.58018359087748</v>
+        <v>-39.06813015575067</v>
       </c>
       <c r="D64">
-        <v>71.41381640912252</v>
+        <v>70.74286984424933</v>
       </c>
       <c r="E64">
-        <v>41.75399999999999</v>
+        <v>43.57099999999998</v>
       </c>
       <c r="F64">
-        <v>112.654</v>
+        <v>114.471</v>
       </c>
       <c r="G64">
         <v>4.66</v>
@@ -6541,37 +6541,37 @@
         <v>2.5</v>
       </c>
       <c r="M64">
-        <v>26.5638132</v>
+        <v>26.9922618</v>
       </c>
       <c r="N64">
-        <v>-24.0638132</v>
+        <v>-24.4922618</v>
       </c>
       <c r="O64">
-        <v>-6.737867696</v>
+        <v>-6.857833304</v>
       </c>
       <c r="P64">
-        <v>-17.325945504</v>
+        <v>-17.634428496</v>
       </c>
       <c r="Q64">
-        <v>0.1740544960000037</v>
+        <v>-0.1344284959999982</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1556203998813575</v>
+        <v>0.1585885187970698</v>
       </c>
       <c r="T64">
-        <v>2.53626789564336</v>
+        <v>2.604815676606694</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02635163840107113</v>
+        <v>0.02593335842645095</v>
       </c>
       <c r="W64">
-        <v>0.2295862836650274</v>
+        <v>0.2296849140830429</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.09411299428953979</v>
+        <v>0.09261913723732484</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2033792478272329</v>
+        <v>0.2052792478272328</v>
       </c>
       <c r="C65">
-        <v>-39.06813015575067</v>
+        <v>-41.54358672206264</v>
       </c>
       <c r="D65">
-        <v>70.74286984424933</v>
+        <v>70.08441327793736</v>
       </c>
       <c r="E65">
-        <v>43.57099999999998</v>
+        <v>45.38799999999999</v>
       </c>
       <c r="F65">
-        <v>114.471</v>
+        <v>116.288</v>
       </c>
       <c r="G65">
         <v>4.66</v>
@@ -6623,37 +6623,37 @@
         <v>2.5</v>
       </c>
       <c r="M65">
-        <v>26.9922618</v>
+        <v>27.4207104</v>
       </c>
       <c r="N65">
-        <v>-24.4922618</v>
+        <v>-24.9207104</v>
       </c>
       <c r="O65">
-        <v>-6.857833304</v>
+        <v>-6.977798912000001</v>
       </c>
       <c r="P65">
-        <v>-17.634428496</v>
+        <v>-17.942911488</v>
       </c>
       <c r="Q65">
-        <v>-0.1344284959999982</v>
+        <v>-0.442911488</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1585885187970698</v>
+        <v>0.1617215332080996</v>
       </c>
       <c r="T65">
-        <v>2.604815676606694</v>
+        <v>2.677171667623547</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02593335842645095</v>
+        <v>0.02552814970103765</v>
       </c>
       <c r="W65">
-        <v>0.2296849140830429</v>
+        <v>0.2297804623004953</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.09261913723732484</v>
+        <v>0.09117196321799159</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2052792478272328</v>
+        <v>0.2071792478272328</v>
       </c>
       <c r="C66">
-        <v>-41.54358672206264</v>
+        <v>-44.00689883472047</v>
       </c>
       <c r="D66">
-        <v>70.08441327793736</v>
+        <v>69.43810116527952</v>
       </c>
       <c r="E66">
-        <v>45.38799999999999</v>
+        <v>47.20499999999998</v>
       </c>
       <c r="F66">
-        <v>116.288</v>
+        <v>118.105</v>
       </c>
       <c r="G66">
         <v>4.66</v>
@@ -6705,37 +6705,37 @@
         <v>2.5</v>
       </c>
       <c r="M66">
-        <v>27.4207104</v>
+        <v>27.849159</v>
       </c>
       <c r="N66">
-        <v>-24.9207104</v>
+        <v>-25.349159</v>
       </c>
       <c r="O66">
-        <v>-6.977798912000001</v>
+        <v>-7.097764520000001</v>
       </c>
       <c r="P66">
-        <v>-17.942911488</v>
+        <v>-18.25139448</v>
       </c>
       <c r="Q66">
-        <v>-0.442911488</v>
+        <v>-0.7513944799999983</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1617215332080996</v>
+        <v>0.1650335770140453</v>
       </c>
       <c r="T66">
-        <v>2.677171667623547</v>
+        <v>2.753662286698505</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02552814970103765</v>
+        <v>0.0251354089364063</v>
       </c>
       <c r="W66">
-        <v>0.2297804623004953</v>
+        <v>0.2298730705727954</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.09117196321799159</v>
+        <v>0.08976931763002249</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2071792478272328</v>
+        <v>0.2090792478272329</v>
       </c>
       <c r="C67">
-        <v>-44.00689883472047</v>
+        <v>-46.45839940876728</v>
       </c>
       <c r="D67">
-        <v>69.43810116527952</v>
+        <v>68.80360059123272</v>
       </c>
       <c r="E67">
-        <v>47.20499999999998</v>
+        <v>49.02199999999999</v>
       </c>
       <c r="F67">
-        <v>118.105</v>
+        <v>119.922</v>
       </c>
       <c r="G67">
         <v>4.66</v>
@@ -6787,37 +6787,37 @@
         <v>2.5</v>
       </c>
       <c r="M67">
-        <v>27.849159</v>
+        <v>28.2776076</v>
       </c>
       <c r="N67">
-        <v>-25.349159</v>
+        <v>-25.7776076</v>
       </c>
       <c r="O67">
-        <v>-7.097764520000001</v>
+        <v>-7.217730128</v>
       </c>
       <c r="P67">
-        <v>-18.25139448</v>
+        <v>-18.559877472</v>
       </c>
       <c r="Q67">
-        <v>-0.7513944799999983</v>
+        <v>-1.059877472</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1650335770140453</v>
+        <v>0.1685404469262231</v>
       </c>
       <c r="T67">
-        <v>2.753662286698505</v>
+        <v>2.834652353954344</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0251354089364063</v>
+        <v>0.02475456940706682</v>
       </c>
       <c r="W67">
-        <v>0.2298730705727954</v>
+        <v>0.2299628725338137</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.08976931763002249</v>
+        <v>0.08840917645381008</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2090792478272329</v>
+        <v>0.2109792478272329</v>
       </c>
       <c r="C68">
-        <v>-46.45839940876728</v>
+        <v>-48.89840930119324</v>
       </c>
       <c r="D68">
-        <v>68.80360059123272</v>
+        <v>68.18059069880677</v>
       </c>
       <c r="E68">
-        <v>49.02199999999999</v>
+        <v>50.839</v>
       </c>
       <c r="F68">
-        <v>119.922</v>
+        <v>121.739</v>
       </c>
       <c r="G68">
         <v>4.66</v>
@@ -6869,37 +6869,37 @@
         <v>2.5</v>
       </c>
       <c r="M68">
-        <v>28.2776076</v>
+        <v>28.7060562</v>
       </c>
       <c r="N68">
-        <v>-25.7776076</v>
+        <v>-26.2060562</v>
       </c>
       <c r="O68">
-        <v>-7.217730128</v>
+        <v>-7.337695736000001</v>
       </c>
       <c r="P68">
-        <v>-18.559877472</v>
+        <v>-18.868360464</v>
       </c>
       <c r="Q68">
-        <v>-1.059877472</v>
+        <v>-1.368360464000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1685404469262231</v>
+        <v>0.1722598544088359</v>
       </c>
       <c r="T68">
-        <v>2.834652353954344</v>
+        <v>2.920550910134779</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02475456940706682</v>
+        <v>0.02438509822188671</v>
       </c>
       <c r="W68">
-        <v>0.2299628725338137</v>
+        <v>0.2300499938392791</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.08840917645381008</v>
+        <v>0.08708963650673829</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2109792478272329</v>
+        <v>0.2128792478272328</v>
       </c>
       <c r="C69">
-        <v>-48.89840930119324</v>
+        <v>-51.32723785195905</v>
       </c>
       <c r="D69">
-        <v>68.18059069880677</v>
+        <v>67.56876214804095</v>
       </c>
       <c r="E69">
-        <v>50.839</v>
+        <v>52.65599999999999</v>
       </c>
       <c r="F69">
-        <v>121.739</v>
+        <v>123.556</v>
       </c>
       <c r="G69">
         <v>4.66</v>
@@ -6951,37 +6951,37 @@
         <v>2.5</v>
       </c>
       <c r="M69">
-        <v>28.7060562</v>
+        <v>29.1345048</v>
       </c>
       <c r="N69">
-        <v>-26.2060562</v>
+        <v>-26.6345048</v>
       </c>
       <c r="O69">
-        <v>-7.337695736000001</v>
+        <v>-7.457661344000002</v>
       </c>
       <c r="P69">
-        <v>-18.868360464</v>
+        <v>-19.176843456</v>
       </c>
       <c r="Q69">
-        <v>-1.368360464000002</v>
+        <v>-1.676843456</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1722598544088359</v>
+        <v>0.176211724859112</v>
       </c>
       <c r="T69">
-        <v>2.920550910134779</v>
+        <v>3.01181812607649</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02438509822188671</v>
+        <v>0.02402649383627073</v>
       </c>
       <c r="W69">
-        <v>0.2300499938392791</v>
+        <v>0.2301345527534074</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.08708963650673829</v>
+        <v>0.0858089065581098</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2128792478272328</v>
+        <v>0.2147792478272329</v>
       </c>
       <c r="C70">
-        <v>-51.32723785195905</v>
+        <v>-53.74518339614903</v>
       </c>
       <c r="D70">
-        <v>67.56876214804095</v>
+        <v>66.96781660385098</v>
       </c>
       <c r="E70">
-        <v>52.65599999999999</v>
+        <v>54.473</v>
       </c>
       <c r="F70">
-        <v>123.556</v>
+        <v>125.373</v>
       </c>
       <c r="G70">
         <v>4.66</v>
@@ -7033,37 +7033,37 @@
         <v>2.5</v>
       </c>
       <c r="M70">
-        <v>29.1345048</v>
+        <v>29.5629534</v>
       </c>
       <c r="N70">
-        <v>-26.6345048</v>
+        <v>-27.0629534</v>
       </c>
       <c r="O70">
-        <v>-7.457661344000002</v>
+        <v>-7.577626952000001</v>
       </c>
       <c r="P70">
-        <v>-19.176843456</v>
+        <v>-19.485326448</v>
       </c>
       <c r="Q70">
-        <v>-1.676843456</v>
+        <v>-1.985326448000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.176211724859112</v>
+        <v>0.1804185546932769</v>
       </c>
       <c r="T70">
-        <v>3.01181812607649</v>
+        <v>3.108973549498313</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02402649383627073</v>
+        <v>0.02367828378067261</v>
       </c>
       <c r="W70">
-        <v>0.2301345527534074</v>
+        <v>0.2302166606845174</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.0858089065581098</v>
+        <v>0.08456529921668787</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2147792478272329</v>
+        <v>0.2166792478272329</v>
       </c>
       <c r="C71">
-        <v>-53.74518339614903</v>
+        <v>-56.15253374903456</v>
       </c>
       <c r="D71">
-        <v>66.96781660385098</v>
+        <v>66.37746625096544</v>
       </c>
       <c r="E71">
-        <v>54.473</v>
+        <v>56.28999999999999</v>
       </c>
       <c r="F71">
-        <v>125.373</v>
+        <v>127.19</v>
       </c>
       <c r="G71">
         <v>4.66</v>
@@ -7115,37 +7115,37 @@
         <v>2.5</v>
       </c>
       <c r="M71">
-        <v>29.5629534</v>
+        <v>29.991402</v>
       </c>
       <c r="N71">
-        <v>-27.0629534</v>
+        <v>-27.491402</v>
       </c>
       <c r="O71">
-        <v>-7.577626952000001</v>
+        <v>-7.697592560000001</v>
       </c>
       <c r="P71">
-        <v>-19.485326448</v>
+        <v>-19.79380944</v>
       </c>
       <c r="Q71">
-        <v>-1.985326448000002</v>
+        <v>-2.29380944</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1804185546932769</v>
+        <v>0.1849058398497195</v>
       </c>
       <c r="T71">
-        <v>3.108973549498313</v>
+        <v>3.212606001148256</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02367828378067261</v>
+        <v>0.02334002258380585</v>
       </c>
       <c r="W71">
-        <v>0.2302166606845174</v>
+        <v>0.2302964226747386</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.08456529921668787</v>
+        <v>0.08335722351359232</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2166792478272329</v>
+        <v>0.2185792478272329</v>
       </c>
       <c r="C72">
-        <v>-56.15253374903456</v>
+        <v>-58.54956666570624</v>
       </c>
       <c r="D72">
-        <v>66.37746625096544</v>
+        <v>65.79743333429377</v>
       </c>
       <c r="E72">
-        <v>56.28999999999999</v>
+        <v>58.107</v>
       </c>
       <c r="F72">
-        <v>127.19</v>
+        <v>129.007</v>
       </c>
       <c r="G72">
         <v>4.66</v>
@@ -7197,37 +7197,37 @@
         <v>2.5</v>
       </c>
       <c r="M72">
-        <v>29.991402</v>
+        <v>30.4198506</v>
       </c>
       <c r="N72">
-        <v>-27.491402</v>
+        <v>-27.9198506</v>
       </c>
       <c r="O72">
-        <v>-7.697592560000001</v>
+        <v>-7.817558168000001</v>
       </c>
       <c r="P72">
-        <v>-19.79380944</v>
+        <v>-20.102292432</v>
       </c>
       <c r="Q72">
-        <v>-2.29380944</v>
+        <v>-2.602292432000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1849058398497195</v>
+        <v>0.1897025929479857</v>
       </c>
       <c r="T72">
-        <v>3.212606001148256</v>
+        <v>3.323385518429231</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02334002258380585</v>
+        <v>0.02301128987135788</v>
       </c>
       <c r="W72">
-        <v>0.2302964226747386</v>
+        <v>0.2303739378483338</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.08335722351359232</v>
+        <v>0.08218317811199238</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2185792478272328</v>
+        <v>0.2204792478272328</v>
       </c>
       <c r="C73">
-        <v>-58.54956666570621</v>
+        <v>-60.93655027681523</v>
       </c>
       <c r="D73">
-        <v>65.79743333429377</v>
+        <v>65.22744972318476</v>
       </c>
       <c r="E73">
-        <v>58.10699999999997</v>
+        <v>59.92399999999998</v>
       </c>
       <c r="F73">
-        <v>129.007</v>
+        <v>130.824</v>
       </c>
       <c r="G73">
         <v>4.66</v>
@@ -7279,37 +7279,37 @@
         <v>2.5</v>
       </c>
       <c r="M73">
-        <v>30.4198506</v>
+        <v>30.8482992</v>
       </c>
       <c r="N73">
-        <v>-27.9198506</v>
+        <v>-28.3482992</v>
       </c>
       <c r="O73">
-        <v>-7.817558168</v>
+        <v>-7.937523776</v>
       </c>
       <c r="P73">
-        <v>-20.102292432</v>
+        <v>-20.410775424</v>
       </c>
       <c r="Q73">
-        <v>-2.602292431999999</v>
+        <v>-2.910775423999997</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1897025929479857</v>
+        <v>0.1948419712675566</v>
       </c>
       <c r="T73">
-        <v>3.32338551842923</v>
+        <v>3.442077858373131</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02301128987135789</v>
+        <v>0.02269168862314459</v>
       </c>
       <c r="W73">
-        <v>0.2303739378483338</v>
+        <v>0.2304492998226625</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.08218317811199249</v>
+        <v>0.08104174508265927</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2204792478272328</v>
+        <v>0.2223792478272328</v>
       </c>
       <c r="C74">
-        <v>-60.93655027681523</v>
+        <v>-63.31374350186178</v>
       </c>
       <c r="D74">
-        <v>65.22744972318476</v>
+        <v>64.66725649813822</v>
       </c>
       <c r="E74">
-        <v>59.92399999999998</v>
+        <v>61.74099999999999</v>
       </c>
       <c r="F74">
-        <v>130.824</v>
+        <v>132.641</v>
       </c>
       <c r="G74">
         <v>4.66</v>
@@ -7361,37 +7361,37 @@
         <v>2.5</v>
       </c>
       <c r="M74">
-        <v>30.8482992</v>
+        <v>31.2767478</v>
       </c>
       <c r="N74">
-        <v>-28.3482992</v>
+        <v>-28.7767478</v>
       </c>
       <c r="O74">
-        <v>-7.937523776</v>
+        <v>-8.057489384</v>
       </c>
       <c r="P74">
-        <v>-20.410775424</v>
+        <v>-20.719258416</v>
       </c>
       <c r="Q74">
-        <v>-2.910775423999997</v>
+        <v>-3.219258415999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1948419712675566</v>
+        <v>0.2003620442774661</v>
       </c>
       <c r="T74">
-        <v>3.442077858373131</v>
+        <v>3.569562223498062</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02269168862314459</v>
+        <v>0.02238084357351246</v>
       </c>
       <c r="W74">
-        <v>0.2304492998226625</v>
+        <v>0.2305225970853658</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.08104174508265927</v>
+        <v>0.0799315841911159</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2223792478272328</v>
+        <v>0.2242792478272329</v>
       </c>
       <c r="C75">
-        <v>-63.31374350186178</v>
+        <v>-65.68139644136762</v>
       </c>
       <c r="D75">
-        <v>64.66725649813822</v>
+        <v>64.11660355863238</v>
       </c>
       <c r="E75">
-        <v>61.74099999999999</v>
+        <v>63.55799999999999</v>
       </c>
       <c r="F75">
-        <v>132.641</v>
+        <v>134.458</v>
       </c>
       <c r="G75">
         <v>4.66</v>
@@ -7443,37 +7443,37 @@
         <v>2.5</v>
       </c>
       <c r="M75">
-        <v>31.2767478</v>
+        <v>31.7051964</v>
       </c>
       <c r="N75">
-        <v>-28.7767478</v>
+        <v>-29.2051964</v>
       </c>
       <c r="O75">
-        <v>-8.057489384</v>
+        <v>-8.177454992000001</v>
       </c>
       <c r="P75">
-        <v>-20.719258416</v>
+        <v>-21.027741408</v>
       </c>
       <c r="Q75">
-        <v>-3.219258415999999</v>
+        <v>-3.527741408000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2003620442774661</v>
+        <v>0.2063067382881378</v>
       </c>
       <c r="T75">
-        <v>3.569562223498062</v>
+        <v>3.706853078247987</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02238084357351246</v>
+        <v>0.02207839974143797</v>
       </c>
       <c r="W75">
-        <v>0.2305225970853658</v>
+        <v>0.2305939133409689</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.0799315841911159</v>
+        <v>0.07885142764799269</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2242792478272329</v>
+        <v>0.2261792478272328</v>
       </c>
       <c r="C76">
-        <v>-65.68139644136762</v>
+        <v>-68.03975074918158</v>
       </c>
       <c r="D76">
-        <v>64.11660355863238</v>
+        <v>63.57524925081839</v>
       </c>
       <c r="E76">
-        <v>63.55799999999999</v>
+        <v>65.37499999999997</v>
       </c>
       <c r="F76">
-        <v>134.458</v>
+        <v>136.275</v>
       </c>
       <c r="G76">
         <v>4.66</v>
@@ -7525,37 +7525,37 @@
         <v>2.5</v>
       </c>
       <c r="M76">
-        <v>31.7051964</v>
+        <v>32.13364499999999</v>
       </c>
       <c r="N76">
-        <v>-29.2051964</v>
+        <v>-29.63364499999999</v>
       </c>
       <c r="O76">
-        <v>-8.177454992000001</v>
+        <v>-8.297420599999999</v>
       </c>
       <c r="P76">
-        <v>-21.027741408</v>
+        <v>-21.3362244</v>
       </c>
       <c r="Q76">
-        <v>-3.527741408000001</v>
+        <v>-3.836224399999995</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2063067382881378</v>
+        <v>0.2127270078196634</v>
       </c>
       <c r="T76">
-        <v>3.706853078247987</v>
+        <v>3.855127201377907</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02207839974143797</v>
+        <v>0.0217840210782188</v>
       </c>
       <c r="W76">
-        <v>0.2305939133409689</v>
+        <v>0.230663327829756</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.07885142764799269</v>
+        <v>0.07780007527935284</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2261792478272328</v>
+        <v>0.2280792478272329</v>
       </c>
       <c r="C77">
-        <v>-68.03975074918158</v>
+        <v>-70.38903998608212</v>
       </c>
       <c r="D77">
-        <v>63.57524925081839</v>
+        <v>63.04296001391786</v>
       </c>
       <c r="E77">
-        <v>65.37499999999997</v>
+        <v>67.19199999999998</v>
       </c>
       <c r="F77">
-        <v>136.275</v>
+        <v>138.092</v>
       </c>
       <c r="G77">
         <v>4.66</v>
@@ -7607,37 +7607,37 @@
         <v>2.5</v>
       </c>
       <c r="M77">
-        <v>32.13364499999999</v>
+        <v>32.5620936</v>
       </c>
       <c r="N77">
-        <v>-29.63364499999999</v>
+        <v>-30.0620936</v>
       </c>
       <c r="O77">
-        <v>-8.297420599999999</v>
+        <v>-8.417386208</v>
       </c>
       <c r="P77">
-        <v>-21.3362244</v>
+        <v>-21.644707392</v>
       </c>
       <c r="Q77">
-        <v>-3.836224399999995</v>
+        <v>-4.144707391999997</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2127270078196634</v>
+        <v>0.2196822998121494</v>
       </c>
       <c r="T77">
-        <v>3.855127201377907</v>
+        <v>4.015757501435321</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0217840210782188</v>
+        <v>0.02149738922192645</v>
       </c>
       <c r="W77">
-        <v>0.230663327829756</v>
+        <v>0.2307309156214697</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.07780007527935284</v>
+        <v>0.07677639007830872</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2280792478272329</v>
+        <v>0.2299792478272329</v>
       </c>
       <c r="C78">
-        <v>-70.38903998608212</v>
+        <v>-72.72948995576377</v>
       </c>
       <c r="D78">
-        <v>63.04296001391786</v>
+        <v>62.51951004423623</v>
       </c>
       <c r="E78">
-        <v>67.19199999999998</v>
+        <v>69.00899999999999</v>
       </c>
       <c r="F78">
-        <v>138.092</v>
+        <v>139.909</v>
       </c>
       <c r="G78">
         <v>4.66</v>
@@ -7689,37 +7689,37 @@
         <v>2.5</v>
       </c>
       <c r="M78">
-        <v>32.5620936</v>
+        <v>32.9905422</v>
       </c>
       <c r="N78">
-        <v>-30.0620936</v>
+        <v>-30.4905422</v>
       </c>
       <c r="O78">
-        <v>-8.417386208</v>
+        <v>-8.537351816000001</v>
       </c>
       <c r="P78">
-        <v>-21.644707392</v>
+        <v>-21.953190384</v>
       </c>
       <c r="Q78">
-        <v>-4.144707391999997</v>
+        <v>-4.453190383999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2196822998121494</v>
+        <v>0.227242399803982</v>
       </c>
       <c r="T78">
-        <v>4.015757501435321</v>
+        <v>4.190355653671639</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02149738922192645</v>
+        <v>0.02121820234891441</v>
       </c>
       <c r="W78">
-        <v>0.2307309156214697</v>
+        <v>0.230796747886126</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.07677639007830872</v>
+        <v>0.07577929410326578</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2299792478272329</v>
+        <v>0.2318792478272329</v>
       </c>
       <c r="C79">
-        <v>-72.72948995576377</v>
+        <v>-75.06131902422318</v>
       </c>
       <c r="D79">
-        <v>62.51951004423623</v>
+        <v>62.00468097577681</v>
       </c>
       <c r="E79">
-        <v>69.00899999999999</v>
+        <v>70.82599999999999</v>
       </c>
       <c r="F79">
-        <v>139.909</v>
+        <v>141.726</v>
       </c>
       <c r="G79">
         <v>4.66</v>
@@ -7771,37 +7771,37 @@
         <v>2.5</v>
       </c>
       <c r="M79">
-        <v>32.9905422</v>
+        <v>33.4189908</v>
       </c>
       <c r="N79">
-        <v>-30.4905422</v>
+        <v>-30.9189908</v>
       </c>
       <c r="O79">
-        <v>-8.537351816000001</v>
+        <v>-8.657317424000002</v>
       </c>
       <c r="P79">
-        <v>-21.953190384</v>
+        <v>-22.261673376</v>
       </c>
       <c r="Q79">
-        <v>-4.453190383999999</v>
+        <v>-4.761673376000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.227242399803982</v>
+        <v>0.2354897816132539</v>
       </c>
       <c r="T79">
-        <v>4.190355653671639</v>
+        <v>4.380826365202168</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02121820234891441</v>
+        <v>0.02094617411367192</v>
       </c>
       <c r="W79">
-        <v>0.230796747886126</v>
+        <v>0.2308608921439962</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.07577929410326578</v>
+        <v>0.07480776469168537</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2318792478272329</v>
+        <v>0.2337792478272329</v>
       </c>
       <c r="C80">
-        <v>-75.06131902422318</v>
+        <v>-77.38473842349397</v>
       </c>
       <c r="D80">
-        <v>62.00468097577681</v>
+        <v>61.49826157650604</v>
       </c>
       <c r="E80">
-        <v>70.82599999999999</v>
+        <v>72.643</v>
       </c>
       <c r="F80">
-        <v>141.726</v>
+        <v>143.543</v>
       </c>
       <c r="G80">
         <v>4.66</v>
@@ -7853,37 +7853,37 @@
         <v>2.5</v>
       </c>
       <c r="M80">
-        <v>33.4189908</v>
+        <v>33.84743940000001</v>
       </c>
       <c r="N80">
-        <v>-30.9189908</v>
+        <v>-31.34743940000001</v>
       </c>
       <c r="O80">
-        <v>-8.657317424000002</v>
+        <v>-8.777283032000003</v>
       </c>
       <c r="P80">
-        <v>-22.261673376</v>
+        <v>-22.570156368</v>
       </c>
       <c r="Q80">
-        <v>-4.761673376000001</v>
+        <v>-5.070156368000003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2354897816132539</v>
+        <v>0.2445226283567422</v>
       </c>
       <c r="T80">
-        <v>4.380826365202168</v>
+        <v>4.58943714449751</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02094617411367192</v>
+        <v>0.02068103266919506</v>
       </c>
       <c r="W80">
-        <v>0.2308608921439962</v>
+        <v>0.2309234124966038</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.07480776469168537</v>
+        <v>0.07386083096141094</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2337792478272329</v>
+        <v>0.2356792478272328</v>
       </c>
       <c r="C81">
-        <v>-77.38473842349397</v>
+        <v>-79.69995254061743</v>
       </c>
       <c r="D81">
-        <v>61.49826157650604</v>
+        <v>61.00004745938256</v>
       </c>
       <c r="E81">
-        <v>72.643</v>
+        <v>74.45999999999998</v>
       </c>
       <c r="F81">
-        <v>143.543</v>
+        <v>145.36</v>
       </c>
       <c r="G81">
         <v>4.66</v>
@@ -7935,37 +7935,37 @@
         <v>2.5</v>
       </c>
       <c r="M81">
-        <v>33.84743940000001</v>
+        <v>34.27588799999999</v>
       </c>
       <c r="N81">
-        <v>-31.34743940000001</v>
+        <v>-31.77588799999999</v>
       </c>
       <c r="O81">
-        <v>-8.777283032000003</v>
+        <v>-8.897248639999999</v>
       </c>
       <c r="P81">
-        <v>-22.570156368</v>
+        <v>-22.87863935999999</v>
       </c>
       <c r="Q81">
-        <v>-5.070156368000003</v>
+        <v>-5.378639359999994</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2445226283567422</v>
+        <v>0.2544587597745792</v>
       </c>
       <c r="T81">
-        <v>4.58943714449751</v>
+        <v>4.818909001722385</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02068103266919506</v>
+        <v>0.02042251976083013</v>
       </c>
       <c r="W81">
-        <v>0.2309234124966038</v>
+        <v>0.2309843698403963</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.07386083096141094</v>
+        <v>0.07293757057439332</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2356792478272328</v>
+        <v>0.2375792478272329</v>
       </c>
       <c r="C82">
-        <v>-79.69995254061743</v>
+        <v>-82.00715919268023</v>
       </c>
       <c r="D82">
-        <v>61.00004745938256</v>
+        <v>60.50984080731975</v>
       </c>
       <c r="E82">
-        <v>74.45999999999998</v>
+        <v>76.27699999999999</v>
       </c>
       <c r="F82">
-        <v>145.36</v>
+        <v>147.177</v>
       </c>
       <c r="G82">
         <v>4.66</v>
@@ -8017,37 +8017,37 @@
         <v>2.5</v>
       </c>
       <c r="M82">
-        <v>34.27588799999999</v>
+        <v>34.7043366</v>
       </c>
       <c r="N82">
-        <v>-31.77588799999999</v>
+        <v>-32.2043366</v>
       </c>
       <c r="O82">
-        <v>-8.897248639999999</v>
+        <v>-9.017214248</v>
       </c>
       <c r="P82">
-        <v>-22.87863935999999</v>
+        <v>-23.187122352</v>
       </c>
       <c r="Q82">
-        <v>-5.378639359999994</v>
+        <v>-5.687122351999996</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2544587597745792</v>
+        <v>0.265440799762715</v>
       </c>
       <c r="T82">
-        <v>4.818909001722385</v>
+        <v>5.072535791286722</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02042251976083013</v>
+        <v>0.02017038988723963</v>
       </c>
       <c r="W82">
-        <v>0.2309843698403963</v>
+        <v>0.2310438220645889</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.07293757057439332</v>
+        <v>0.07203710674014152</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2375792478272329</v>
+        <v>0.2394792478272328</v>
       </c>
       <c r="C83">
-        <v>-82.00715919268023</v>
+        <v>-84.30654988869604</v>
       </c>
       <c r="D83">
-        <v>60.50984080731975</v>
+        <v>60.02745011130396</v>
       </c>
       <c r="E83">
-        <v>76.27699999999999</v>
+        <v>78.09399999999999</v>
       </c>
       <c r="F83">
-        <v>147.177</v>
+        <v>148.994</v>
       </c>
       <c r="G83">
         <v>4.66</v>
@@ -8099,37 +8099,37 @@
         <v>2.5</v>
       </c>
       <c r="M83">
-        <v>34.7043366</v>
+        <v>35.1327852</v>
       </c>
       <c r="N83">
-        <v>-32.2043366</v>
+        <v>-32.6327852</v>
       </c>
       <c r="O83">
-        <v>-9.017214248</v>
+        <v>-9.137179856000001</v>
       </c>
       <c r="P83">
-        <v>-23.187122352</v>
+        <v>-23.495605344</v>
       </c>
       <c r="Q83">
-        <v>-5.687122351999996</v>
+        <v>-5.995605343999998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.265440799762715</v>
+        <v>0.2776430664161992</v>
       </c>
       <c r="T83">
-        <v>5.072535791286722</v>
+        <v>5.354343335247095</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02017038988723963</v>
+        <v>0.0199244095227611</v>
       </c>
       <c r="W83">
-        <v>0.2310438220645889</v>
+        <v>0.2311018242345329</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.07203710674014152</v>
+        <v>0.07115860543843244</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2394792478272328</v>
+        <v>0.2413792478272329</v>
       </c>
       <c r="C84">
-        <v>-84.30654988869604</v>
+        <v>-86.59831007906</v>
       </c>
       <c r="D84">
-        <v>60.02745011130396</v>
+        <v>59.55268992094</v>
       </c>
       <c r="E84">
-        <v>78.09399999999999</v>
+        <v>79.911</v>
       </c>
       <c r="F84">
-        <v>148.994</v>
+        <v>150.811</v>
       </c>
       <c r="G84">
         <v>4.66</v>
@@ -8181,37 +8181,37 @@
         <v>2.5</v>
       </c>
       <c r="M84">
-        <v>35.1327852</v>
+        <v>35.5612338</v>
       </c>
       <c r="N84">
-        <v>-32.6327852</v>
+        <v>-33.0612338</v>
       </c>
       <c r="O84">
-        <v>-9.137179856000001</v>
+        <v>-9.257145464000002</v>
       </c>
       <c r="P84">
-        <v>-23.495605344</v>
+        <v>-23.804088336</v>
       </c>
       <c r="Q84">
-        <v>-5.995605343999998</v>
+        <v>-6.304088336</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2776430664161992</v>
+        <v>0.2912808938524462</v>
       </c>
       <c r="T84">
-        <v>5.354343335247095</v>
+        <v>5.669304707908688</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0199244095227611</v>
+        <v>0.01968435639598084</v>
       </c>
       <c r="W84">
-        <v>0.2311018242345329</v>
+        <v>0.2311584287618277</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.07115860543843244</v>
+        <v>0.07030127284278875</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2413792478272329</v>
+        <v>0.2432792478272329</v>
       </c>
       <c r="C85">
-        <v>-86.59831007906</v>
+        <v>-88.88261939325828</v>
       </c>
       <c r="D85">
-        <v>59.55268992094</v>
+        <v>59.08538060674173</v>
       </c>
       <c r="E85">
-        <v>79.911</v>
+        <v>81.72800000000001</v>
       </c>
       <c r="F85">
-        <v>150.811</v>
+        <v>152.628</v>
       </c>
       <c r="G85">
         <v>4.66</v>
@@ -8263,37 +8263,37 @@
         <v>2.5</v>
       </c>
       <c r="M85">
-        <v>35.5612338</v>
+        <v>35.98968240000001</v>
       </c>
       <c r="N85">
-        <v>-33.0612338</v>
+        <v>-33.48968240000001</v>
       </c>
       <c r="O85">
-        <v>-9.257145464000002</v>
+        <v>-9.377111072000003</v>
       </c>
       <c r="P85">
-        <v>-23.804088336</v>
+        <v>-24.112571328</v>
       </c>
       <c r="Q85">
-        <v>-6.304088336</v>
+        <v>-6.612571328000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2912808938524462</v>
+        <v>0.3066234497182242</v>
       </c>
       <c r="T85">
-        <v>5.669304707908688</v>
+        <v>6.023636252152984</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01968435639598084</v>
+        <v>0.01945001881983821</v>
       </c>
       <c r="W85">
-        <v>0.2311584287618277</v>
+        <v>0.2312136855622822</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.07030127284278875</v>
+        <v>0.06946435292799358</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2432792478272329</v>
+        <v>0.2451792478272329</v>
       </c>
       <c r="C86">
-        <v>-88.88261939325824</v>
+        <v>-91.15965186647286</v>
       </c>
       <c r="D86">
-        <v>59.08538060674175</v>
+        <v>58.62534813352714</v>
       </c>
       <c r="E86">
-        <v>81.72799999999998</v>
+        <v>83.54499999999999</v>
       </c>
       <c r="F86">
-        <v>152.628</v>
+        <v>154.445</v>
       </c>
       <c r="G86">
         <v>4.66</v>
@@ -8345,37 +8345,37 @@
         <v>2.5</v>
       </c>
       <c r="M86">
-        <v>35.9896824</v>
+        <v>36.418131</v>
       </c>
       <c r="N86">
-        <v>-33.4896824</v>
+        <v>-33.918131</v>
       </c>
       <c r="O86">
-        <v>-9.377111072</v>
+        <v>-9.497076680000001</v>
       </c>
       <c r="P86">
-        <v>-24.112571328</v>
+        <v>-24.42105432</v>
       </c>
       <c r="Q86">
-        <v>-6.612571328000001</v>
+        <v>-6.921054320000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.306623449718224</v>
+        <v>0.3240116796994389</v>
       </c>
       <c r="T86">
-        <v>6.023636252152979</v>
+        <v>6.425212002296512</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01945001881983821</v>
+        <v>0.01922119506901658</v>
       </c>
       <c r="W86">
-        <v>0.2312136855622822</v>
+        <v>0.2312676422027259</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.06946435292799358</v>
+        <v>0.06864712524648775</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2451792478272329</v>
+        <v>0.2470792478272328</v>
       </c>
       <c r="C87">
-        <v>-91.15965186647286</v>
+        <v>-93.4295761556825</v>
       </c>
       <c r="D87">
-        <v>58.62534813352714</v>
+        <v>58.17242384431751</v>
       </c>
       <c r="E87">
-        <v>83.54499999999999</v>
+        <v>85.36199999999999</v>
       </c>
       <c r="F87">
-        <v>154.445</v>
+        <v>156.262</v>
       </c>
       <c r="G87">
         <v>4.66</v>
@@ -8427,37 +8427,37 @@
         <v>2.5</v>
       </c>
       <c r="M87">
-        <v>36.418131</v>
+        <v>36.8465796</v>
       </c>
       <c r="N87">
-        <v>-33.918131</v>
+        <v>-34.3465796</v>
       </c>
       <c r="O87">
-        <v>-9.497076680000001</v>
+        <v>-9.617042288</v>
       </c>
       <c r="P87">
-        <v>-24.42105432</v>
+        <v>-24.729537312</v>
       </c>
       <c r="Q87">
-        <v>-6.921054320000003</v>
+        <v>-7.229537311999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3240116796994389</v>
+        <v>0.3438839425351131</v>
       </c>
       <c r="T87">
-        <v>6.425212002296512</v>
+        <v>6.884155716746262</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01922119506901658</v>
+        <v>0.01899769280077221</v>
       </c>
       <c r="W87">
-        <v>0.2312676422027259</v>
+        <v>0.2313203440375779</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.06864712524648775</v>
+        <v>0.06784890285990075</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2470792478272328</v>
+        <v>0.2489792478272329</v>
       </c>
       <c r="C88">
-        <v>-93.4295761556825</v>
+        <v>-95.69255574582279</v>
       </c>
       <c r="D88">
-        <v>58.17242384431751</v>
+        <v>57.7264442541772</v>
       </c>
       <c r="E88">
-        <v>85.36199999999999</v>
+        <v>87.17899999999997</v>
       </c>
       <c r="F88">
-        <v>156.262</v>
+        <v>158.079</v>
       </c>
       <c r="G88">
         <v>4.66</v>
@@ -8509,37 +8509,37 @@
         <v>2.5</v>
       </c>
       <c r="M88">
-        <v>36.8465796</v>
+        <v>37.27502819999999</v>
       </c>
       <c r="N88">
-        <v>-34.3465796</v>
+        <v>-34.77502819999999</v>
       </c>
       <c r="O88">
-        <v>-9.617042288</v>
+        <v>-9.737007896</v>
       </c>
       <c r="P88">
-        <v>-24.729537312</v>
+        <v>-25.03802030399999</v>
       </c>
       <c r="Q88">
-        <v>-7.229537311999998</v>
+        <v>-7.538020303999993</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3438839425351131</v>
+        <v>0.3668134765762757</v>
       </c>
       <c r="T88">
-        <v>6.884155716746262</v>
+        <v>7.413706156495974</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01899769280077221</v>
+        <v>0.01877932851570586</v>
       </c>
       <c r="W88">
-        <v>0.2313203440375779</v>
+        <v>0.2313718343359966</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.06784890285990075</v>
+        <v>0.0670690304132352</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2489792478272329</v>
+        <v>0.2508792478272329</v>
       </c>
       <c r="C89">
-        <v>-95.69255574582279</v>
+        <v>-97.9487491465356</v>
       </c>
       <c r="D89">
-        <v>57.7264442541772</v>
+        <v>57.28725085346439</v>
       </c>
       <c r="E89">
-        <v>87.17899999999997</v>
+        <v>88.99599999999998</v>
       </c>
       <c r="F89">
-        <v>158.079</v>
+        <v>159.896</v>
       </c>
       <c r="G89">
         <v>4.66</v>
@@ -8591,37 +8591,37 @@
         <v>2.5</v>
       </c>
       <c r="M89">
-        <v>37.27502819999999</v>
+        <v>37.7034768</v>
       </c>
       <c r="N89">
-        <v>-34.77502819999999</v>
+        <v>-35.2034768</v>
       </c>
       <c r="O89">
-        <v>-9.737007896</v>
+        <v>-9.856973504000001</v>
       </c>
       <c r="P89">
-        <v>-25.03802030399999</v>
+        <v>-25.34650329599999</v>
       </c>
       <c r="Q89">
-        <v>-7.538020303999993</v>
+        <v>-7.846503295999995</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3668134765762757</v>
+        <v>0.3935645996242987</v>
       </c>
       <c r="T89">
-        <v>7.413706156495974</v>
+        <v>8.031515002870641</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01877932851570586</v>
+        <v>0.01856592705530011</v>
       </c>
       <c r="W89">
-        <v>0.2313718343359966</v>
+        <v>0.2314221544003602</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.0670690304132352</v>
+        <v>0.06630688234035753</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2508792478272329</v>
+        <v>0.2527792478272329</v>
       </c>
       <c r="C90">
-        <v>-97.9487491465356</v>
+        <v>-100.1983100800046</v>
       </c>
       <c r="D90">
-        <v>57.28725085346439</v>
+        <v>56.85468991999534</v>
       </c>
       <c r="E90">
-        <v>88.99599999999998</v>
+        <v>90.81299999999999</v>
       </c>
       <c r="F90">
-        <v>159.896</v>
+        <v>161.713</v>
       </c>
       <c r="G90">
         <v>4.66</v>
@@ -8673,37 +8673,37 @@
         <v>2.5</v>
       </c>
       <c r="M90">
-        <v>37.7034768</v>
+        <v>38.1319254</v>
       </c>
       <c r="N90">
-        <v>-35.2034768</v>
+        <v>-35.6319254</v>
       </c>
       <c r="O90">
-        <v>-9.856973504000001</v>
+        <v>-9.976939112</v>
       </c>
       <c r="P90">
-        <v>-25.34650329599999</v>
+        <v>-25.654986288</v>
       </c>
       <c r="Q90">
-        <v>-7.846503295999995</v>
+        <v>-8.154986288</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3935645996242987</v>
+        <v>0.4251795632265077</v>
       </c>
       <c r="T90">
-        <v>8.031515002870641</v>
+        <v>8.761652730404336</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01856592705530011</v>
+        <v>0.01835732113333045</v>
       </c>
       <c r="W90">
-        <v>0.2314221544003602</v>
+        <v>0.2314713436767607</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.06630688234035753</v>
+        <v>0.06556186119046592</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2527792478272329</v>
+        <v>0.2546792478272328</v>
       </c>
       <c r="C91">
-        <v>-100.1983100800046</v>
+        <v>-102.4413876603451</v>
       </c>
       <c r="D91">
-        <v>56.85468991999534</v>
+        <v>56.42861233965485</v>
       </c>
       <c r="E91">
-        <v>90.81299999999999</v>
+        <v>92.63</v>
       </c>
       <c r="F91">
-        <v>161.713</v>
+        <v>163.53</v>
       </c>
       <c r="G91">
         <v>4.66</v>
@@ -8755,37 +8755,37 @@
         <v>2.5</v>
       </c>
       <c r="M91">
-        <v>38.1319254</v>
+        <v>38.560374</v>
       </c>
       <c r="N91">
-        <v>-35.6319254</v>
+        <v>-36.060374</v>
       </c>
       <c r="O91">
-        <v>-9.976939112</v>
+        <v>-10.09690472</v>
       </c>
       <c r="P91">
-        <v>-25.654986288</v>
+        <v>-25.96346928</v>
       </c>
       <c r="Q91">
-        <v>-8.154986288</v>
+        <v>-8.463469280000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4251795632265077</v>
+        <v>0.4631175195491585</v>
       </c>
       <c r="T91">
-        <v>8.761652730404336</v>
+        <v>9.637818003444769</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01835732113333045</v>
+        <v>0.01815335089851566</v>
       </c>
       <c r="W91">
-        <v>0.2314713436767607</v>
+        <v>0.23151943985813</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.06556186119046592</v>
+        <v>0.06483339606612737</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2546792478272328</v>
+        <v>0.2565792478272328</v>
       </c>
       <c r="C92">
-        <v>-102.4413876603451</v>
+        <v>-104.6781265649873</v>
       </c>
       <c r="D92">
-        <v>56.42861233965485</v>
+        <v>56.0088734350127</v>
       </c>
       <c r="E92">
-        <v>92.63</v>
+        <v>94.447</v>
       </c>
       <c r="F92">
-        <v>163.53</v>
+        <v>165.347</v>
       </c>
       <c r="G92">
         <v>4.66</v>
@@ -8837,37 +8837,37 @@
         <v>2.5</v>
       </c>
       <c r="M92">
-        <v>38.560374</v>
+        <v>38.98882260000001</v>
       </c>
       <c r="N92">
-        <v>-36.060374</v>
+        <v>-36.48882260000001</v>
       </c>
       <c r="O92">
-        <v>-10.09690472</v>
+        <v>-10.216870328</v>
       </c>
       <c r="P92">
-        <v>-25.96346928</v>
+        <v>-26.271952272</v>
       </c>
       <c r="Q92">
-        <v>-8.463469280000002</v>
+        <v>-8.771952272000004</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4631175195491585</v>
+        <v>0.5094861328323984</v>
       </c>
       <c r="T92">
-        <v>9.637818003444769</v>
+        <v>10.70868667049419</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01815335089851566</v>
+        <v>0.0179538635260045</v>
       </c>
       <c r="W92">
-        <v>0.23151943985813</v>
+        <v>0.2315664789805681</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.06483339606612737</v>
+        <v>0.06412094116430178</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2565792478272328</v>
+        <v>0.2584792478272329</v>
       </c>
       <c r="C93">
-        <v>-104.6781265649873</v>
+        <v>-106.9086671984672</v>
       </c>
       <c r="D93">
-        <v>56.0088734350127</v>
+        <v>55.59533280153282</v>
       </c>
       <c r="E93">
-        <v>94.447</v>
+        <v>96.26399999999998</v>
       </c>
       <c r="F93">
-        <v>165.347</v>
+        <v>167.164</v>
       </c>
       <c r="G93">
         <v>4.66</v>
@@ -8919,37 +8919,37 @@
         <v>2.5</v>
       </c>
       <c r="M93">
-        <v>38.98882260000001</v>
+        <v>39.4172712</v>
       </c>
       <c r="N93">
-        <v>-36.48882260000001</v>
+        <v>-36.9172712</v>
       </c>
       <c r="O93">
-        <v>-10.216870328</v>
+        <v>-10.336835936</v>
       </c>
       <c r="P93">
-        <v>-26.271952272</v>
+        <v>-26.580435264</v>
       </c>
       <c r="Q93">
-        <v>-8.771952272000004</v>
+        <v>-9.080435264000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5094861328323984</v>
+        <v>0.5674468994364483</v>
       </c>
       <c r="T93">
-        <v>10.70868667049419</v>
+        <v>12.04727250430597</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0179538635260045</v>
+        <v>0.01775871283550445</v>
       </c>
       <c r="W93">
-        <v>0.2315664789805681</v>
+        <v>0.2316124955133881</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.06412094116430178</v>
+        <v>0.0634239744125159</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2584792478272329</v>
+        <v>0.2603792478272329</v>
       </c>
       <c r="C94">
-        <v>-106.9086671984672</v>
+        <v>-109.1331458490148</v>
       </c>
       <c r="D94">
-        <v>55.59533280153282</v>
+        <v>55.18785415098518</v>
       </c>
       <c r="E94">
-        <v>96.26399999999998</v>
+        <v>98.08099999999999</v>
       </c>
       <c r="F94">
-        <v>167.164</v>
+        <v>168.981</v>
       </c>
       <c r="G94">
         <v>4.66</v>
@@ -9001,37 +9001,37 @@
         <v>2.5</v>
       </c>
       <c r="M94">
-        <v>39.4172712</v>
+        <v>39.8457198</v>
       </c>
       <c r="N94">
-        <v>-36.9172712</v>
+        <v>-37.3457198</v>
       </c>
       <c r="O94">
-        <v>-10.336835936</v>
+        <v>-10.456801544</v>
       </c>
       <c r="P94">
-        <v>-26.580435264</v>
+        <v>-26.888918256</v>
       </c>
       <c r="Q94">
-        <v>-9.080435264000002</v>
+        <v>-9.388918255999997</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5674468994364483</v>
+        <v>0.6419678850702267</v>
       </c>
       <c r="T94">
-        <v>12.04727250430597</v>
+        <v>13.76831143349253</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01775871283550445</v>
+        <v>0.01756775893404742</v>
       </c>
       <c r="W94">
-        <v>0.2316124955133881</v>
+        <v>0.2316575224433516</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.0634239744125159</v>
+        <v>0.06274199619302645</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2603792478272329</v>
+        <v>0.2622792478272329</v>
       </c>
       <c r="C95">
-        <v>-109.1331458490148</v>
+        <v>-111.3516948383063</v>
       </c>
       <c r="D95">
-        <v>55.18785415098518</v>
+        <v>54.7863051616937</v>
       </c>
       <c r="E95">
-        <v>98.08099999999999</v>
+        <v>99.898</v>
       </c>
       <c r="F95">
-        <v>168.981</v>
+        <v>170.798</v>
       </c>
       <c r="G95">
         <v>4.66</v>
@@ -9083,37 +9083,37 @@
         <v>2.5</v>
       </c>
       <c r="M95">
-        <v>39.8457198</v>
+        <v>40.2741684</v>
       </c>
       <c r="N95">
-        <v>-37.3457198</v>
+        <v>-37.7741684</v>
       </c>
       <c r="O95">
-        <v>-10.456801544</v>
+        <v>-10.576767152</v>
       </c>
       <c r="P95">
-        <v>-26.888918256</v>
+        <v>-27.197401248</v>
       </c>
       <c r="Q95">
-        <v>-9.388918255999997</v>
+        <v>-9.697401247999998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6419678850702267</v>
+        <v>0.741329199248598</v>
       </c>
       <c r="T95">
-        <v>13.76831143349253</v>
+        <v>16.06303000574129</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01756775893404742</v>
+        <v>0.01738086788155755</v>
       </c>
       <c r="W95">
-        <v>0.2316575224433516</v>
+        <v>0.2317015913535287</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.06274199619302645</v>
+        <v>0.06207452814841985</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2622792478272329</v>
+        <v>0.2641792478272329</v>
       </c>
       <c r="C96">
-        <v>-111.3516948383063</v>
+        <v>-113.5644426647253</v>
       </c>
       <c r="D96">
-        <v>54.7863051616937</v>
+        <v>54.39055733527473</v>
       </c>
       <c r="E96">
-        <v>99.898</v>
+        <v>101.715</v>
       </c>
       <c r="F96">
-        <v>170.798</v>
+        <v>172.615</v>
       </c>
       <c r="G96">
         <v>4.66</v>
@@ -9165,37 +9165,37 @@
         <v>2.5</v>
       </c>
       <c r="M96">
-        <v>40.2741684</v>
+        <v>40.702617</v>
       </c>
       <c r="N96">
-        <v>-37.7741684</v>
+        <v>-38.202617</v>
       </c>
       <c r="O96">
-        <v>-10.576767152</v>
+        <v>-10.69673276</v>
       </c>
       <c r="P96">
-        <v>-27.197401248</v>
+        <v>-27.50588424</v>
       </c>
       <c r="Q96">
-        <v>-9.697401247999998</v>
+        <v>-10.00588424</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.741329199248598</v>
+        <v>0.880435039098318</v>
       </c>
       <c r="T96">
-        <v>16.06303000574129</v>
+        <v>19.27563600688956</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01738086788155755</v>
+        <v>0.01719791137754115</v>
       </c>
       <c r="W96">
-        <v>0.2317015913535287</v>
+        <v>0.2317447324971758</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.06207452814841985</v>
+        <v>0.061421112062647</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2641792478272329</v>
+        <v>0.2660792478272329</v>
       </c>
       <c r="C97">
-        <v>-113.5644426647253</v>
+        <v>-115.7715141404601</v>
       </c>
       <c r="D97">
-        <v>54.39055733527473</v>
+        <v>54.00048585953989</v>
       </c>
       <c r="E97">
-        <v>101.715</v>
+        <v>103.532</v>
       </c>
       <c r="F97">
-        <v>172.615</v>
+        <v>174.432</v>
       </c>
       <c r="G97">
         <v>4.66</v>
@@ -9247,37 +9247,37 @@
         <v>2.5</v>
       </c>
       <c r="M97">
-        <v>40.702617</v>
+        <v>41.13106560000001</v>
       </c>
       <c r="N97">
-        <v>-38.202617</v>
+        <v>-38.63106560000001</v>
       </c>
       <c r="O97">
-        <v>-10.69673276</v>
+        <v>-10.816698368</v>
       </c>
       <c r="P97">
-        <v>-27.50588424</v>
+        <v>-27.814367232</v>
       </c>
       <c r="Q97">
-        <v>-10.00588424</v>
+        <v>-10.314367232</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.880435039098318</v>
+        <v>1.089093798872898</v>
       </c>
       <c r="T97">
-        <v>19.27563600688956</v>
+        <v>24.09454500861196</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01719791137754115</v>
+        <v>0.01701876646735843</v>
       </c>
       <c r="W97">
-        <v>0.2317447324971758</v>
+        <v>0.2317869748669969</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.061421112062647</v>
+        <v>0.06078130881199439</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2660792478272329</v>
+        <v>0.2679792478272329</v>
       </c>
       <c r="C98">
-        <v>-115.7715141404601</v>
+        <v>-117.9730305227437</v>
       </c>
       <c r="D98">
-        <v>54.00048585953989</v>
+        <v>53.61596947725629</v>
       </c>
       <c r="E98">
-        <v>103.532</v>
+        <v>105.349</v>
       </c>
       <c r="F98">
-        <v>174.432</v>
+        <v>176.249</v>
       </c>
       <c r="G98">
         <v>4.66</v>
@@ -9329,37 +9329,37 @@
         <v>2.5</v>
       </c>
       <c r="M98">
-        <v>41.1310656</v>
+        <v>41.5595142</v>
       </c>
       <c r="N98">
-        <v>-38.6310656</v>
+        <v>-39.0595142</v>
       </c>
       <c r="O98">
-        <v>-10.816698368</v>
+        <v>-10.936663976</v>
       </c>
       <c r="P98">
-        <v>-27.814367232</v>
+        <v>-28.122850224</v>
       </c>
       <c r="Q98">
-        <v>-10.314367232</v>
+        <v>-10.622850224</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.089093798872895</v>
+        <v>1.436858398497194</v>
       </c>
       <c r="T98">
-        <v>24.0945450086119</v>
+        <v>32.12606001148254</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01701876646735843</v>
+        <v>0.01684331526666402</v>
       </c>
       <c r="W98">
-        <v>0.2317869748669969</v>
+        <v>0.2318283462601206</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.06078130881199439</v>
+        <v>0.06015469738094292</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2679792478272329</v>
+        <v>0.2698792478272329</v>
       </c>
       <c r="C99">
-        <v>-117.9730305227437</v>
+        <v>-120.1691096395257</v>
       </c>
       <c r="D99">
-        <v>53.61596947725629</v>
+        <v>53.23689036047423</v>
       </c>
       <c r="E99">
-        <v>105.349</v>
+        <v>107.166</v>
       </c>
       <c r="F99">
-        <v>176.249</v>
+        <v>178.066</v>
       </c>
       <c r="G99">
         <v>4.66</v>
@@ -9411,37 +9411,37 @@
         <v>2.5</v>
       </c>
       <c r="M99">
-        <v>41.5595142</v>
+        <v>41.9879628</v>
       </c>
       <c r="N99">
-        <v>-39.0595142</v>
+        <v>-39.4879628</v>
       </c>
       <c r="O99">
-        <v>-10.936663976</v>
+        <v>-11.056629584</v>
       </c>
       <c r="P99">
-        <v>-28.122850224</v>
+        <v>-28.431333216</v>
       </c>
       <c r="Q99">
-        <v>-10.622850224</v>
+        <v>-10.931333216</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.436858398497194</v>
+        <v>2.13238759774579</v>
       </c>
       <c r="T99">
-        <v>32.12606001148254</v>
+        <v>48.1890900172238</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01684331526666402</v>
+        <v>0.01667144470271847</v>
       </c>
       <c r="W99">
-        <v>0.2318283462601206</v>
+        <v>0.231868873339099</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.06015469738094292</v>
+        <v>0.05954087393828023</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2698792478272329</v>
+        <v>0.2717792478272329</v>
       </c>
       <c r="C100">
-        <v>-120.1691096395257</v>
+        <v>-122.3598660098516</v>
       </c>
       <c r="D100">
-        <v>53.23689036047423</v>
+        <v>52.86313399014841</v>
       </c>
       <c r="E100">
-        <v>107.166</v>
+        <v>108.983</v>
       </c>
       <c r="F100">
-        <v>178.066</v>
+        <v>179.883</v>
       </c>
       <c r="G100">
         <v>4.66</v>
@@ -9493,37 +9493,37 @@
         <v>2.5</v>
       </c>
       <c r="M100">
-        <v>41.9879628</v>
+        <v>42.41641139999999</v>
       </c>
       <c r="N100">
-        <v>-39.4879628</v>
+        <v>-39.91641139999999</v>
       </c>
       <c r="O100">
-        <v>-11.056629584</v>
+        <v>-11.176595192</v>
       </c>
       <c r="P100">
-        <v>-28.431333216</v>
+        <v>-28.73981620799999</v>
       </c>
       <c r="Q100">
-        <v>-10.931333216</v>
+        <v>-11.23981620799999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.13238759774579</v>
+        <v>4.218975195491581</v>
       </c>
       <c r="T100">
-        <v>48.1890900172238</v>
+        <v>96.3781800344476</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01667144470271847</v>
+        <v>0.01650304627137788</v>
       </c>
       <c r="W100">
-        <v>0.231868873339099</v>
+        <v>0.2319085816892091</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.05954087393828023</v>
+        <v>0.05893945096920672</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2717792478272329</v>
-      </c>
-      <c r="C101">
-        <v>-122.3598660098516</v>
-      </c>
-      <c r="D101">
-        <v>52.86313399014841</v>
-      </c>
-      <c r="E101">
-        <v>108.983</v>
-      </c>
-      <c r="F101">
-        <v>179.883</v>
-      </c>
-      <c r="G101">
-        <v>4.66</v>
-      </c>
-      <c r="H101">
-        <v>110.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>20</v>
-      </c>
-      <c r="K101">
-        <v>17.5</v>
-      </c>
-      <c r="L101">
-        <v>2.5</v>
-      </c>
-      <c r="M101">
-        <v>42.41641139999999</v>
-      </c>
-      <c r="N101">
-        <v>-39.91641139999999</v>
-      </c>
-      <c r="O101">
-        <v>-11.176595192</v>
-      </c>
-      <c r="P101">
-        <v>-28.73981620799999</v>
-      </c>
-      <c r="Q101">
-        <v>-11.23981620799999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.218975195491581</v>
-      </c>
-      <c r="T101">
-        <v>96.3781800344476</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01650304627137788</v>
-      </c>
-      <c r="W101">
-        <v>0.2319085816892091</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.05893945096920672</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
